--- a/data/analysis/momentumNew/mergeTtestResult/merged_t_test.xlsx
+++ b/data/analysis/momentumNew/mergeTtestResult/merged_t_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Han\學習\金融策略\分析程式\data\analysis\momentumNew\mergeTtestResult\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{82F48FF3-B50E-4F12-9727-201521F988D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B00524-421A-4D13-AA67-B05EDD2B73A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{79B926A8-815C-4ADE-A3A1-103001E1D343}"/>
   </bookViews>
@@ -18,12 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">merged_t_test!$A$1:$G$49</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="48">
   <si>
     <t>remark</t>
   </si>
@@ -55,7 +55,120 @@
     <t>winner - loser</t>
   </si>
   <si>
-    <t>J</t>
+    <t>(0.45)</t>
+  </si>
+  <si>
+    <t>(3.14)</t>
+  </si>
+  <si>
+    <t>(2.69)</t>
+  </si>
+  <si>
+    <t>(-0.54)</t>
+  </si>
+  <si>
+    <t>(1.77)</t>
+  </si>
+  <si>
+    <t>(2.18)</t>
+  </si>
+  <si>
+    <t>(0.05)</t>
+  </si>
+  <si>
+    <t>(3.23)</t>
+  </si>
+  <si>
+    <t>(2.89)</t>
+  </si>
+  <si>
+    <t>(1.35)</t>
+  </si>
+  <si>
+    <t>(4.18)</t>
+  </si>
+  <si>
+    <t>(2.98)</t>
+  </si>
+  <si>
+    <t>(1.20)</t>
+  </si>
+  <si>
+    <t>(3.61)</t>
+  </si>
+  <si>
+    <t>(2.71)</t>
+  </si>
+  <si>
+    <t>(1.53)</t>
+  </si>
+  <si>
+    <t>(2.67)</t>
+  </si>
+  <si>
+    <t>(1.26)</t>
+  </si>
+  <si>
+    <t>(0.04)</t>
+  </si>
+  <si>
+    <t>(0.09)</t>
+  </si>
+  <si>
+    <t>(0.79)</t>
+  </si>
+  <si>
+    <t>(3.18)</t>
+  </si>
+  <si>
+    <t>(2.48)</t>
+  </si>
+  <si>
+    <t>(1.98)</t>
+  </si>
+  <si>
+    <t>(3.27)</t>
+  </si>
+  <si>
+    <t>(1.37)</t>
+  </si>
+  <si>
+    <t>(-0.05)</t>
+  </si>
+  <si>
+    <t>(0.97)</t>
+  </si>
+  <si>
+    <t>(2.13)</t>
+  </si>
+  <si>
+    <t>(1.59)</t>
+  </si>
+  <si>
+    <t>(1.91)</t>
+  </si>
+  <si>
+    <t>(2.25)</t>
+  </si>
+  <si>
+    <t>(1.57)</t>
+  </si>
+  <si>
+    <t>(0.93)</t>
+  </si>
+  <si>
+    <t>(0.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K = </t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>J =</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panel A</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -64,9 +177,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="186" formatCode="0.0000"/>
+    <numFmt numFmtId="176" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -251,8 +364,16 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -444,8 +565,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -593,6 +720,200 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dashDotDot">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="dashDotDot">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </right>
+      <top style="dashDotDot">
+        <color theme="2" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -725,7 +1046,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -741,59 +1062,173 @@
     <xf numFmtId="10" fontId="18" fillId="33" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="20" fillId="34" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="20" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="20" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="20" fillId="34" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="20" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="35" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -841,7 +1276,7 @@
     <cellStyle name="壞" xfId="8" builtinId="27" customBuiltin="1"/>
     <cellStyle name="警告文字" xfId="15" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -855,36 +1290,6 @@
     <dxf>
       <font>
         <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
       </font>
     </dxf>
   </dxfs>
@@ -1197,19 +1602,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{828DFD01-9D50-4EA6-A7DD-A0B766D34BA5}">
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="17.375" style="10" customWidth="1"/>
-    <col min="4" max="4" width="8.625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="13.25" style="16" customWidth="1"/>
-    <col min="6" max="6" width="16" style="10" customWidth="1"/>
-    <col min="7" max="7" width="15.75" style="10" customWidth="1"/>
-    <col min="8" max="9" width="9" style="5"/>
-    <col min="10" max="10" width="15.375" style="5" customWidth="1"/>
-    <col min="11" max="14" width="12.625" style="5" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="5"/>
+    <col min="1" max="2" width="11.375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="17.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="8.625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="13.25" style="13" customWidth="1"/>
+    <col min="6" max="6" width="16" style="8" customWidth="1"/>
+    <col min="7" max="7" width="15.75" style="8" customWidth="1"/>
+    <col min="10" max="10" width="15.375" customWidth="1"/>
+    <col min="11" max="14" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1235,1605 +1638,1679 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
         <v>3</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="6">
         <v>3</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="6">
         <v>114</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="11">
         <v>3.0260421823129999E-4</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="9">
         <v>2.8355084394913299E-2</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="9">
         <v>0.97742896460482598</v>
       </c>
     </row>
-    <row r="3" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
         <v>3</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="6">
         <v>3</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="6">
         <v>114</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="11">
         <v>3.0722210317410001E-2</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="9">
         <v>3.54698888875836</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="9">
         <v>5.6845064904419997E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="8">
+      <c r="C4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6">
         <v>114</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="11">
         <v>3.0419606099178698E-2</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="9">
         <v>3.5780818191419801</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="9">
         <v>5.1106356269530005E-4</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
+      <c r="I4" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="40"/>
+    </row>
+    <row r="5" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="7">
         <v>6</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="7">
         <v>111</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="12">
         <v>1.51301049852723E-2</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="10">
         <v>1.1443893939324601</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="10">
         <v>0.25494625406830401</v>
       </c>
-      <c r="I5" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18">
+      <c r="I5" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="15">
         <v>3</v>
       </c>
-      <c r="L5" s="18">
+      <c r="L5" s="15">
         <v>6</v>
       </c>
-      <c r="M5" s="18">
-        <v>9</v>
-      </c>
-      <c r="N5" s="18">
+      <c r="M5" s="15">
+        <v>9</v>
+      </c>
+      <c r="N5" s="42">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
         <v>3</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="7">
         <v>6</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="7">
         <v>111</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="12">
         <v>6.5631060309720005E-2</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="10">
         <v>4.6891959760591497</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="10">
         <v>7.9232025762956804E-6</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="43">
         <v>3</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="21">
         <f>$E2</f>
         <v>3.0260421823129999E-4</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="21">
         <f>$E5</f>
         <v>1.51301049852723E-2</v>
       </c>
-      <c r="M6" s="17">
+      <c r="M6" s="21">
         <f>$E8</f>
         <v>1.51244575442856E-2</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="44">
         <f>$E11</f>
         <v>2.3280515551955899E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>3</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="9">
+      <c r="C7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="7">
         <v>111</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="12">
         <v>5.0500955324447698E-2</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="10">
         <v>3.8236782043989401</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="10">
         <v>2.184178713642E-4</v>
       </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="19" t="str">
+      <c r="I7" s="45"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="25" t="str">
         <f>"("&amp;TEXT($F2, "0.00")&amp;")"</f>
         <v>(0.03)</v>
       </c>
-      <c r="L7" s="19" t="str">
+      <c r="L7" s="25" t="str">
         <f>"("&amp;TEXT($F5, "0.00")&amp;")"</f>
         <v>(1.14)</v>
       </c>
-      <c r="M7" s="19" t="str">
+      <c r="M7" s="25" t="str">
         <f>"("&amp;TEXT($F8, "0.00")&amp;")"</f>
         <v>(0.96)</v>
       </c>
-      <c r="N7" s="19" t="str">
+      <c r="N7" s="46" t="str">
         <f>"("&amp;TEXT($F11, "0.00")&amp;")"</f>
         <v>(1.16)</v>
       </c>
     </row>
-    <row r="8" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>3</v>
       </c>
-      <c r="B8" s="8">
-        <v>9</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="6">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>108</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="11">
         <v>1.51244575442856E-2</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="9">
         <v>0.95653052500906299</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="9">
         <v>0.34096046080184</v>
       </c>
-      <c r="I8" s="10">
-        <v>3</v>
-      </c>
-      <c r="J8" s="10" t="s">
+      <c r="I8" s="45"/>
+      <c r="J8" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="47">
         <f>$E3</f>
         <v>3.0722210317410001E-2</v>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="47">
         <f>$E6</f>
         <v>6.5631060309720005E-2</v>
       </c>
-      <c r="M8" s="17">
+      <c r="M8" s="47">
         <f>$E9</f>
         <v>9.0526528336692905E-2</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="48">
         <f>$E12</f>
         <v>9.33097832882889E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <v>3</v>
       </c>
-      <c r="B9" s="8">
-        <v>9</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="6">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <v>108</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="11">
         <v>9.0526528336692905E-2</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="9">
         <v>5.1462038766068803</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="9">
         <v>1.2141876138480901E-6</v>
       </c>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="19" t="str">
+      <c r="I9" s="45"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="36" t="str">
         <f>"("&amp;TEXT($F3,"0.00")&amp;")"</f>
         <v>(3.55)</v>
       </c>
-      <c r="L9" s="19" t="str">
+      <c r="L9" s="36" t="str">
         <f>"("&amp;TEXT($F6,"0.00")&amp;")"</f>
         <v>(4.69)</v>
       </c>
-      <c r="M9" s="19" t="str">
+      <c r="M9" s="36" t="str">
         <f>"("&amp;TEXT($F9,"0.00")&amp;")"</f>
         <v>(5.15)</v>
       </c>
-      <c r="N9" s="19" t="str">
+      <c r="N9" s="49" t="str">
         <f>"("&amp;TEXT($F12,"0.00")&amp;")"</f>
         <v>(4.41)</v>
       </c>
     </row>
-    <row r="10" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <v>3</v>
       </c>
-      <c r="B10" s="7">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="8">
+      <c r="B10" s="5">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="6">
         <v>108</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="11">
         <v>7.5402070792407294E-2</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="9">
         <v>4.4945377822361303</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="9">
         <v>1.7724280876774E-5</v>
       </c>
-      <c r="I10" s="11">
-        <v>3</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="17">
+      <c r="I10" s="45"/>
+      <c r="J10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="47">
         <f>$E4</f>
         <v>3.0419606099178698E-2</v>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="47">
         <f>$E7</f>
         <v>5.0500955324447698E-2</v>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="47">
         <f>$E10</f>
         <v>7.5402070792407294E-2</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="48">
         <f>$E13</f>
         <v>7.0029267736333001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
         <v>3</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="7">
         <v>12</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="7">
         <v>105</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="12">
         <v>2.3280515551955899E-2</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="10">
         <v>1.1620071159640999</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="10">
         <v>0.24789234222405299</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="21" t="str">
+      <c r="I11" s="50"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="37" t="str">
         <f>"("&amp;TEXT($F4,"0.00")&amp;")"</f>
         <v>(3.58)</v>
       </c>
-      <c r="L11" s="21" t="str">
+      <c r="L11" s="37" t="str">
         <f>"("&amp;TEXT($F7,"0.00")&amp;")"</f>
         <v>(3.82)</v>
       </c>
-      <c r="M11" s="21" t="str">
+      <c r="M11" s="37" t="str">
         <f>"("&amp;TEXT($F10,"0.00")&amp;")"</f>
         <v>(4.49)</v>
       </c>
-      <c r="N11" s="21" t="str">
+      <c r="N11" s="51" t="str">
         <f>"("&amp;TEXT($F13,"0.00")&amp;")"</f>
         <v>(3.39)</v>
       </c>
     </row>
-    <row r="12" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
         <v>3</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="7">
         <v>12</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="7">
         <v>105</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="12">
         <v>9.33097832882889E-2</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="10">
         <v>4.4123635783784998</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="10">
         <v>2.5034503907783899E-5</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="52">
         <v>6</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="K12" s="17">
-        <f>$E8</f>
-        <v>1.51244575442856E-2</v>
-      </c>
-      <c r="L12" s="17">
-        <f>$E11</f>
-        <v>2.3280515551955899E-2</v>
-      </c>
-      <c r="M12" s="17">
-        <f>$E14</f>
+      <c r="K12" s="21">
         <v>4.7735012474096001E-3</v>
       </c>
-      <c r="N12" s="17">
-        <f>$E17</f>
+      <c r="L12" s="21">
         <v>1.89783044088855E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M12" s="21">
+        <v>1.99711867006667E-2</v>
+      </c>
+      <c r="N12" s="44">
+        <v>3.0649711185840801E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>3</v>
       </c>
       <c r="B13" s="2">
         <v>12</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="9">
+      <c r="C13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="7">
         <v>105</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="12">
         <v>7.0029267736333001E-2</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="10">
         <v>3.3910500846225302</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="10">
         <v>9.8533179837500011E-4</v>
       </c>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="19" t="str">
-        <f>"("&amp;TEXT($F8, "0.00")&amp;")"</f>
-        <v>(0.96)</v>
-      </c>
-      <c r="L13" s="19" t="str">
-        <f>"("&amp;TEXT($F11, "0.00")&amp;")"</f>
-        <v>(1.16)</v>
-      </c>
-      <c r="M13" s="19" t="str">
-        <f>"("&amp;TEXT($F14, "0.00")&amp;")"</f>
-        <v>(0.45)</v>
-      </c>
-      <c r="N13" s="19" t="str">
-        <f>"("&amp;TEXT($F17, "0.00")&amp;")"</f>
-        <v>(1.35)</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+      <c r="I13" s="45"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="M13" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>6</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>3</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="6">
         <v>111</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="11">
         <v>4.7735012474096001E-3</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="9">
         <v>0.44911286122773603</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="9">
         <v>0.65423383389473</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="45"/>
+      <c r="J14" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="47">
+        <v>2.7115683765055399E-2</v>
+      </c>
+      <c r="L14" s="47">
+        <v>5.4315765000363898E-2</v>
+      </c>
+      <c r="M14" s="47">
+        <v>6.03256929965394E-2</v>
+      </c>
+      <c r="N14" s="48">
+        <v>5.3065850483251402E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
         <v>6</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="B15" s="6">
+        <v>3</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="17">
-        <f>$E9</f>
-        <v>9.0526528336692905E-2</v>
-      </c>
-      <c r="L14" s="17">
-        <f>$E12</f>
-        <v>9.33097832882889E-2</v>
-      </c>
-      <c r="M14" s="17">
-        <f>$E15</f>
+      <c r="D15" s="6">
+        <v>111</v>
+      </c>
+      <c r="E15" s="11">
         <v>2.7115683765055399E-2</v>
       </c>
-      <c r="N14" s="17">
-        <f>$E18</f>
+      <c r="F15" s="9">
+        <v>3.13615113483938</v>
+      </c>
+      <c r="G15" s="9">
+        <v>2.1961835765053998E-3</v>
+      </c>
+      <c r="I15" s="45"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="49" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>6</v>
+      </c>
+      <c r="B16" s="5">
+        <v>3</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="6">
+        <v>111</v>
+      </c>
+      <c r="E16" s="11">
+        <v>2.23421825176458E-2</v>
+      </c>
+      <c r="F16" s="9">
+        <v>2.6870396316370502</v>
+      </c>
+      <c r="G16" s="9">
+        <v>8.3279350537053005E-3</v>
+      </c>
+      <c r="I16" s="45"/>
+      <c r="J16" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="47">
+        <v>2.23421825176458E-2</v>
+      </c>
+      <c r="L16" s="47">
+        <v>3.5337460591478298E-2</v>
+      </c>
+      <c r="M16" s="47">
+        <v>4.0354506295872603E-2</v>
+      </c>
+      <c r="N16" s="44">
+        <v>2.2416139297410601E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>6</v>
+      </c>
+      <c r="B17" s="7">
+        <v>6</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="7">
+        <v>108</v>
+      </c>
+      <c r="E17" s="12">
+        <v>1.89783044088855E-2</v>
+      </c>
+      <c r="F17" s="10">
+        <v>1.34747042886984</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0.18067514945157101</v>
+      </c>
+      <c r="I17" s="50"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="L17" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="N17" s="53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>6</v>
+      </c>
+      <c r="B18" s="7">
+        <v>6</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="7">
+        <v>108</v>
+      </c>
+      <c r="E18" s="12">
         <v>5.4315765000363898E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
-        <v>6</v>
-      </c>
-      <c r="B15" s="8">
-        <v>3</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="8">
-        <v>111</v>
-      </c>
-      <c r="E15" s="14">
-        <v>2.7115683765055399E-2</v>
-      </c>
-      <c r="F15" s="12">
-        <v>3.13615113483938</v>
-      </c>
-      <c r="G15" s="12">
-        <v>2.1961835765053998E-3</v>
-      </c>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="19" t="str">
-        <f>"("&amp;TEXT($F9,"0.00")&amp;")"</f>
-        <v>(5.15)</v>
-      </c>
-      <c r="L15" s="19" t="str">
-        <f>"("&amp;TEXT($F12,"0.00")&amp;")"</f>
-        <v>(4.41)</v>
-      </c>
-      <c r="M15" s="19" t="str">
-        <f>"("&amp;TEXT($F15,"0.00")&amp;")"</f>
-        <v>(3.14)</v>
-      </c>
-      <c r="N15" s="19" t="str">
-        <f>"("&amp;TEXT($F18,"0.00")&amp;")"</f>
-        <v>(4.18)</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>6</v>
-      </c>
-      <c r="B16" s="7">
-        <v>3</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="8">
-        <v>111</v>
-      </c>
-      <c r="E16" s="14">
-        <v>2.23421825176458E-2</v>
-      </c>
-      <c r="F16" s="12">
-        <v>2.6870396316370502</v>
-      </c>
-      <c r="G16" s="12">
-        <v>8.3279350537053005E-3</v>
-      </c>
-      <c r="I16" s="11">
-        <v>6</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="17">
-        <f>$E10</f>
-        <v>7.5402070792407294E-2</v>
-      </c>
-      <c r="L16" s="17">
-        <f>$E13</f>
-        <v>7.0029267736333001E-2</v>
-      </c>
-      <c r="M16" s="17">
-        <f>$E16</f>
-        <v>2.23421825176458E-2</v>
-      </c>
-      <c r="N16" s="17">
-        <f>$E19</f>
-        <v>3.5337460591478298E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
-        <v>6</v>
-      </c>
-      <c r="B17" s="9">
-        <v>6</v>
-      </c>
-      <c r="C17" s="9" t="s">
+      <c r="F18" s="10">
+        <v>4.1771525637975904</v>
+      </c>
+      <c r="G18" s="10">
+        <v>6.0419980721123302E-5</v>
+      </c>
+      <c r="I18" s="52">
+        <v>9</v>
+      </c>
+      <c r="J18" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="9">
-        <v>108</v>
-      </c>
-      <c r="E17" s="15">
-        <v>1.89783044088855E-2</v>
-      </c>
-      <c r="F17" s="13">
-        <v>1.34747042886984</v>
-      </c>
-      <c r="G17" s="13">
-        <v>0.18067514945157101</v>
-      </c>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="21" t="str">
-        <f>"("&amp;TEXT($F10,"0.00")&amp;")"</f>
-        <v>(4.49)</v>
-      </c>
-      <c r="L17" s="21" t="str">
-        <f>"("&amp;TEXT($F13,"0.00")&amp;")"</f>
-        <v>(3.39)</v>
-      </c>
-      <c r="M17" s="21" t="str">
-        <f>"("&amp;TEXT($F16,"0.00")&amp;")"</f>
-        <v>(2.69)</v>
-      </c>
-      <c r="N17" s="21" t="str">
-        <f>"("&amp;TEXT($F19,"0.00")&amp;")"</f>
-        <v>(2.98)</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
-        <v>6</v>
-      </c>
-      <c r="B18" s="9">
-        <v>6</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="9">
-        <v>108</v>
-      </c>
-      <c r="E18" s="15">
-        <v>5.4315765000363898E-2</v>
-      </c>
-      <c r="F18" s="13">
-        <v>4.1771525637975904</v>
-      </c>
-      <c r="G18" s="13">
-        <v>6.0419980721123302E-5</v>
-      </c>
-      <c r="I18" s="10">
-        <v>9</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="K18" s="17">
-        <f>$E14</f>
-        <v>4.7735012474096001E-3</v>
-      </c>
-      <c r="L18" s="17">
-        <f>$E17</f>
-        <v>1.89783044088855E-2</v>
-      </c>
-      <c r="M18" s="17">
-        <f>$E20</f>
-        <v>1.99711867006667E-2</v>
-      </c>
-      <c r="N18" s="17">
-        <f>$E23</f>
-        <v>3.0649711185840801E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K18" s="21">
+        <v>5.9719290995810005E-4</v>
+      </c>
+      <c r="L18" s="21">
+        <v>6.1873933427599999E-4</v>
+      </c>
+      <c r="M18" s="21">
+        <v>1.523367447362E-3</v>
+      </c>
+      <c r="N18" s="44">
+        <v>1.5399793559194999E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>6</v>
       </c>
       <c r="B19" s="2">
         <v>6</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="9">
+      <c r="C19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="7">
         <v>108</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="12">
         <v>3.5337460591478298E-2</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="10">
         <v>2.98291024159405</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="10">
         <v>3.5367985366198001E-3</v>
       </c>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="19" t="str">
-        <f>"("&amp;TEXT($F14, "0.00")&amp;")"</f>
-        <v>(0.45)</v>
-      </c>
-      <c r="L19" s="19" t="str">
-        <f>"("&amp;TEXT($F17, "0.00")&amp;")"</f>
-        <v>(1.35)</v>
-      </c>
-      <c r="M19" s="19" t="str">
-        <f>"("&amp;TEXT($F20, "0.00")&amp;")"</f>
-        <v>(1.20)</v>
-      </c>
-      <c r="N19" s="19" t="str">
-        <f>"("&amp;TEXT($F23, "0.00")&amp;")"</f>
-        <v>(1.53)</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+      <c r="I19" s="45"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="L19" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="M19" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="N19" s="46" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
         <v>6</v>
       </c>
-      <c r="B20" s="8">
-        <v>9</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="B20" s="6">
+        <v>9</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="6">
         <v>105</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="11">
         <v>1.99711867006667E-2</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="9">
         <v>1.20457814144487</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="9">
         <v>0.231100321207518</v>
       </c>
-      <c r="I20" s="10">
-        <v>9</v>
-      </c>
-      <c r="J20" s="10" t="s">
+      <c r="I20" s="45"/>
+      <c r="J20" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="17">
-        <f>$E15</f>
-        <v>2.7115683765055399E-2</v>
-      </c>
-      <c r="L20" s="17">
-        <f>$E18</f>
-        <v>5.4315765000363898E-2</v>
-      </c>
-      <c r="M20" s="17">
-        <f>$E21</f>
+      <c r="K20" s="47">
+        <v>2.8474975298435901E-2</v>
+      </c>
+      <c r="L20" s="47">
+        <v>4.1623593254200397E-2</v>
+      </c>
+      <c r="M20" s="47">
+        <v>4.0294606718451698E-2</v>
+      </c>
+      <c r="N20" s="48">
+        <v>4.1963339851818701E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>6</v>
+      </c>
+      <c r="B21" s="6">
+        <v>9</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="6">
+        <v>105</v>
+      </c>
+      <c r="E21" s="11">
         <v>6.03256929965394E-2</v>
       </c>
-      <c r="N20" s="17">
-        <f>$E24</f>
+      <c r="F21" s="9">
+        <v>3.6065100358000701</v>
+      </c>
+      <c r="G21" s="9">
+        <v>4.7856639655370002E-4</v>
+      </c>
+      <c r="I21" s="45"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="L21" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="M21" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="N21" s="49" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>6</v>
+      </c>
+      <c r="B22" s="5">
+        <v>9</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="6">
+        <v>105</v>
+      </c>
+      <c r="E22" s="11">
+        <v>4.0354506295872603E-2</v>
+      </c>
+      <c r="F22" s="9">
+        <v>2.7064255503855201</v>
+      </c>
+      <c r="G22" s="9">
+        <v>7.9506872459265999E-3</v>
+      </c>
+      <c r="I22" s="45"/>
+      <c r="J22" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="47">
+        <v>2.7877782388477702E-2</v>
+      </c>
+      <c r="L22" s="47">
+        <v>4.1004853919924297E-2</v>
+      </c>
+      <c r="M22" s="47">
+        <v>3.8771239271089601E-2</v>
+      </c>
+      <c r="N22" s="44">
+        <v>2.6563546292623599E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>6</v>
+      </c>
+      <c r="B23" s="7">
+        <v>12</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="7">
+        <v>102</v>
+      </c>
+      <c r="E23" s="12">
+        <v>3.0649711185840801E-2</v>
+      </c>
+      <c r="F23" s="10">
+        <v>1.5309333480479801</v>
+      </c>
+      <c r="G23" s="10">
+        <v>0.12891208974354801</v>
+      </c>
+      <c r="I23" s="50"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="M23" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="N23" s="53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>6</v>
+      </c>
+      <c r="B24" s="7">
+        <v>12</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="7">
+        <v>102</v>
+      </c>
+      <c r="E24" s="12">
         <v>5.3065850483251402E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+      <c r="F24" s="10">
+        <v>2.6749590287444098</v>
+      </c>
+      <c r="G24" s="10">
+        <v>8.7196464352812999E-3</v>
+      </c>
+      <c r="I24" s="52">
+        <v>12</v>
+      </c>
+      <c r="J24" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="K24" s="21">
+        <v>-6.2206069450507998E-3</v>
+      </c>
+      <c r="L24" s="21">
+        <v>-6.9457633388909999E-4</v>
+      </c>
+      <c r="M24" s="21">
+        <v>1.7274350360729E-2</v>
+      </c>
+      <c r="N24" s="48">
+        <v>4.7582304856785398E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
         <v>6</v>
       </c>
-      <c r="B21" s="8">
-        <v>9</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="B25" s="7">
+        <v>12</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="7">
+        <v>102</v>
+      </c>
+      <c r="E25" s="12">
+        <v>2.2416139297410601E-2</v>
+      </c>
+      <c r="F25" s="10">
+        <v>1.2647026514538</v>
+      </c>
+      <c r="G25" s="10">
+        <v>0.208888402471089</v>
+      </c>
+      <c r="I25" s="45"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="L25" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="M25" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" s="54" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>9</v>
+      </c>
+      <c r="B26" s="6">
+        <v>3</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="6">
+        <v>108</v>
+      </c>
+      <c r="E26" s="11">
+        <v>5.9719290995810005E-4</v>
+      </c>
+      <c r="F26" s="9">
+        <v>5.2714981072726597E-2</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0.95805729432186704</v>
+      </c>
+      <c r="I26" s="45"/>
+      <c r="J26" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="8">
+      <c r="K26" s="21">
+        <v>1.55610672921839E-2</v>
+      </c>
+      <c r="L26" s="21">
+        <v>2.14332070845108E-2</v>
+      </c>
+      <c r="M26" s="21">
+        <v>3.3700752615642197E-2</v>
+      </c>
+      <c r="N26" s="48">
+        <v>5.05347405509049E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>9</v>
+      </c>
+      <c r="B27" s="6">
+        <v>3</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="6">
+        <v>108</v>
+      </c>
+      <c r="E27" s="11">
+        <v>2.8474975298435901E-2</v>
+      </c>
+      <c r="F27" s="9">
+        <v>3.2314643208591001</v>
+      </c>
+      <c r="G27" s="9">
+        <v>1.6370331429953E-3</v>
+      </c>
+      <c r="I27" s="45"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="L27" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="M27" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="N27" s="54" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>9</v>
+      </c>
+      <c r="B28" s="5">
+        <v>3</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="6">
+        <v>108</v>
+      </c>
+      <c r="E28" s="11">
+        <v>2.7877782388477702E-2</v>
+      </c>
+      <c r="F28" s="9">
+        <v>2.8904916757838102</v>
+      </c>
+      <c r="G28" s="9">
+        <v>4.6583346619845003E-3</v>
+      </c>
+      <c r="I28" s="45"/>
+      <c r="J28" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="47">
+        <v>2.1781674237234702E-2</v>
+      </c>
+      <c r="L28" s="60">
+        <v>2.21277834183999E-2</v>
+      </c>
+      <c r="M28" s="60">
+        <v>1.6426402254913201E-2</v>
+      </c>
+      <c r="N28" s="44">
+        <v>2.9524356941194999E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>6</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="7">
         <v>105</v>
       </c>
-      <c r="E21" s="14">
-        <v>6.03256929965394E-2</v>
-      </c>
-      <c r="F21" s="12">
-        <v>3.6065100358000701</v>
-      </c>
-      <c r="G21" s="12">
-        <v>4.7856639655370002E-4</v>
-      </c>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="19" t="str">
-        <f>"("&amp;TEXT($F15,"0.00")&amp;")"</f>
-        <v>(3.14)</v>
-      </c>
-      <c r="L21" s="19" t="str">
-        <f>"("&amp;TEXT($F18,"0.00")&amp;")"</f>
-        <v>(4.18)</v>
-      </c>
-      <c r="M21" s="19" t="str">
-        <f>"("&amp;TEXT($F21,"0.00")&amp;")"</f>
-        <v>(3.61)</v>
-      </c>
-      <c r="N21" s="19" t="str">
-        <f>"("&amp;TEXT($F24,"0.00")&amp;")"</f>
-        <v>(2.67)</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+      <c r="E29" s="12">
+        <v>6.1873933427599999E-4</v>
+      </c>
+      <c r="F29" s="10">
+        <v>4.4346786661663397E-2</v>
+      </c>
+      <c r="G29" s="10">
+        <v>0.96471301456515401</v>
+      </c>
+      <c r="I29" s="55"/>
+      <c r="J29" s="56"/>
+      <c r="K29" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="L29" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="M29" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="N29" s="59" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
         <v>6</v>
       </c>
-      <c r="B22" s="7">
-        <v>9</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="8">
+      <c r="C30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="7">
         <v>105</v>
       </c>
-      <c r="E22" s="14">
-        <v>4.0354506295872603E-2</v>
-      </c>
-      <c r="F22" s="12">
-        <v>2.7064255503855201</v>
-      </c>
-      <c r="G22" s="12">
-        <v>7.9506872459265999E-3</v>
-      </c>
-      <c r="I22" s="11">
-        <v>9</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="17">
-        <f>$E16</f>
-        <v>2.23421825176458E-2</v>
-      </c>
-      <c r="L22" s="17">
-        <f>$E19</f>
-        <v>3.5337460591478298E-2</v>
-      </c>
-      <c r="M22" s="17">
-        <f>$E22</f>
-        <v>4.0354506295872603E-2</v>
-      </c>
-      <c r="N22" s="17">
-        <f>$E25</f>
-        <v>2.2416139297410601E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9">
-        <v>6</v>
-      </c>
-      <c r="B23" s="9">
-        <v>12</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="9">
-        <v>102</v>
-      </c>
-      <c r="E23" s="15">
-        <v>3.0649711185840801E-2</v>
-      </c>
-      <c r="F23" s="13">
-        <v>1.5309333480479801</v>
-      </c>
-      <c r="G23" s="13">
-        <v>0.12891208974354801</v>
-      </c>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="21" t="str">
-        <f>"("&amp;TEXT($F16,"0.00")&amp;")"</f>
-        <v>(2.69)</v>
-      </c>
-      <c r="L23" s="21" t="str">
-        <f>"("&amp;TEXT($F19,"0.00")&amp;")"</f>
-        <v>(2.98)</v>
-      </c>
-      <c r="M23" s="21" t="str">
-        <f>"("&amp;TEXT($F22,"0.00")&amp;")"</f>
-        <v>(2.71)</v>
-      </c>
-      <c r="N23" s="21" t="str">
-        <f>"("&amp;TEXT($F25,"0.00")&amp;")"</f>
-        <v>(1.26)</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="9">
-        <v>6</v>
-      </c>
-      <c r="B24" s="9">
-        <v>12</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="9">
-        <v>102</v>
-      </c>
-      <c r="E24" s="15">
-        <v>5.3065850483251402E-2</v>
-      </c>
-      <c r="F24" s="13">
-        <v>2.6749590287444098</v>
-      </c>
-      <c r="G24" s="13">
-        <v>8.7196464352812999E-3</v>
-      </c>
-      <c r="I24" s="10">
-        <v>12</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="K24" s="17">
-        <f>$E20</f>
-        <v>1.99711867006667E-2</v>
-      </c>
-      <c r="L24" s="17">
-        <f>$E23</f>
-        <v>3.0649711185840801E-2</v>
-      </c>
-      <c r="M24" s="17">
-        <f>$E26</f>
-        <v>5.9719290995810005E-4</v>
-      </c>
-      <c r="N24" s="17">
-        <f>$E29</f>
-        <v>6.1873933427599999E-4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
-        <v>6</v>
-      </c>
-      <c r="B25" s="9">
-        <v>12</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="9">
-        <v>102</v>
-      </c>
-      <c r="E25" s="15">
-        <v>2.2416139297410601E-2</v>
-      </c>
-      <c r="F25" s="13">
-        <v>1.2647026514538</v>
-      </c>
-      <c r="G25" s="13">
-        <v>0.208888402471089</v>
-      </c>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="19" t="str">
-        <f>"("&amp;TEXT($F20, "0.00")&amp;")"</f>
-        <v>(1.20)</v>
-      </c>
-      <c r="L25" s="19" t="str">
-        <f>"("&amp;TEXT($F23, "0.00")&amp;")"</f>
-        <v>(1.53)</v>
-      </c>
-      <c r="M25" s="19" t="str">
-        <f>"("&amp;TEXT($F26, "0.00")&amp;")"</f>
-        <v>(0.05)</v>
-      </c>
-      <c r="N25" s="19" t="str">
-        <f>"("&amp;TEXT($F29, "0.00")&amp;")"</f>
-        <v>(0.04)</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
-        <v>9</v>
-      </c>
-      <c r="B26" s="8">
-        <v>3</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="8">
-        <v>108</v>
-      </c>
-      <c r="E26" s="14">
-        <v>5.9719290995810005E-4</v>
-      </c>
-      <c r="F26" s="12">
-        <v>5.2714981072726597E-2</v>
-      </c>
-      <c r="G26" s="12">
-        <v>0.95805729432186704</v>
-      </c>
-      <c r="I26" s="10">
-        <v>12</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="K26" s="17">
-        <f>$E21</f>
-        <v>6.03256929965394E-2</v>
-      </c>
-      <c r="L26" s="17">
-        <f>$E24</f>
-        <v>5.3065850483251402E-2</v>
-      </c>
-      <c r="M26" s="17">
-        <f>$E27</f>
-        <v>2.8474975298435901E-2</v>
-      </c>
-      <c r="N26" s="17">
-        <f>$E30</f>
+      <c r="E30" s="12">
         <v>4.1623593254200397E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
-        <v>9</v>
-      </c>
-      <c r="B27" s="8">
-        <v>3</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="8">
-        <v>108</v>
-      </c>
-      <c r="E27" s="14">
-        <v>2.8474975298435901E-2</v>
-      </c>
-      <c r="F27" s="12">
-        <v>3.2314643208591001</v>
-      </c>
-      <c r="G27" s="12">
-        <v>1.6370331429953E-3</v>
-      </c>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="19" t="str">
-        <f>"("&amp;TEXT($F21,"0.00")&amp;")"</f>
-        <v>(3.61)</v>
-      </c>
-      <c r="L27" s="19" t="str">
-        <f>"("&amp;TEXT($F24,"0.00")&amp;")"</f>
-        <v>(2.67)</v>
-      </c>
-      <c r="M27" s="19" t="str">
-        <f>"("&amp;TEXT($F27,"0.00")&amp;")"</f>
-        <v>(3.23)</v>
-      </c>
-      <c r="N27" s="19" t="str">
-        <f>"("&amp;TEXT($F30,"0.00")&amp;")"</f>
-        <v>(3.18)</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <v>9</v>
-      </c>
-      <c r="B28" s="7">
-        <v>3</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="8">
-        <v>108</v>
-      </c>
-      <c r="E28" s="14">
-        <v>2.7877782388477702E-2</v>
-      </c>
-      <c r="F28" s="12">
-        <v>2.8904916757838102</v>
-      </c>
-      <c r="G28" s="12">
-        <v>4.6583346619845003E-3</v>
-      </c>
-      <c r="I28" s="11">
-        <v>12</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="K28" s="17">
-        <f>$E22</f>
-        <v>4.0354506295872603E-2</v>
-      </c>
-      <c r="L28" s="17">
-        <f>$E25</f>
-        <v>2.2416139297410601E-2</v>
-      </c>
-      <c r="M28" s="17">
-        <f>$E28</f>
-        <v>2.7877782388477702E-2</v>
-      </c>
-      <c r="N28" s="17">
-        <f>$E31</f>
-        <v>4.1004853919924297E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
-        <v>9</v>
-      </c>
-      <c r="B29" s="9">
-        <v>6</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="9">
-        <v>105</v>
-      </c>
-      <c r="E29" s="15">
-        <v>6.1873933427599999E-4</v>
-      </c>
-      <c r="F29" s="13">
-        <v>4.4346786661663397E-2</v>
-      </c>
-      <c r="G29" s="13">
-        <v>0.96471301456515401</v>
-      </c>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="21" t="str">
-        <f>"("&amp;TEXT($F22,"0.00")&amp;")"</f>
-        <v>(2.71)</v>
-      </c>
-      <c r="L29" s="21" t="str">
-        <f>"("&amp;TEXT($F25,"0.00")&amp;")"</f>
-        <v>(1.26)</v>
-      </c>
-      <c r="M29" s="21" t="str">
-        <f>"("&amp;TEXT($F28,"0.00")&amp;")"</f>
-        <v>(2.89)</v>
-      </c>
-      <c r="N29" s="21" t="str">
-        <f>"("&amp;TEXT($F31,"0.00")&amp;")"</f>
-        <v>(3.27)</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
-        <v>9</v>
-      </c>
-      <c r="B30" s="9">
-        <v>6</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="9">
-        <v>105</v>
-      </c>
-      <c r="E30" s="15">
-        <v>4.1623593254200397E-2</v>
-      </c>
-      <c r="F30" s="13">
+      <c r="F30" s="10">
         <v>3.1788306862105702</v>
       </c>
-      <c r="G30" s="13">
+      <c r="G30" s="10">
         <v>1.9481016183373E-3</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K30" s="17"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>9</v>
       </c>
       <c r="B31" s="2">
         <v>6</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="9">
+      <c r="C31" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="7">
         <v>105</v>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="12">
         <v>4.1004853919924297E-2</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="10">
         <v>3.2691054510320399</v>
       </c>
-      <c r="G31" s="13">
+      <c r="G31" s="10">
         <v>1.4631170676755001E-3</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8">
-        <v>9</v>
-      </c>
-      <c r="B32" s="8">
-        <v>9</v>
-      </c>
-      <c r="C32" s="8" t="s">
+      <c r="K31" s="18"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>9</v>
+      </c>
+      <c r="B32" s="6">
+        <v>9</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="6">
         <v>102</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="11">
         <v>1.523367447362E-3</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="9">
         <v>9.0674662684546395E-2</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="9">
         <v>0.92793068806257695</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8">
-        <v>9</v>
-      </c>
-      <c r="B33" s="8">
-        <v>9</v>
-      </c>
-      <c r="C33" s="8" t="s">
+      <c r="K32" s="17"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>9</v>
+      </c>
+      <c r="B33" s="6">
+        <v>9</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="6">
         <v>102</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="11">
         <v>4.0294606718451698E-2</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="9">
         <v>2.4803654449841401</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="9">
         <v>1.47777782253665E-2</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
-        <v>9</v>
-      </c>
-      <c r="B34" s="7">
-        <v>9</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="8">
+      <c r="K33" s="18"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>9</v>
+      </c>
+      <c r="B34" s="5">
+        <v>9</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="6">
         <v>102</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="11">
         <v>3.8771239271089601E-2</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="9">
         <v>2.4818415957859701</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="9">
         <v>1.4720291072391501E-2</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="9">
-        <v>9</v>
-      </c>
-      <c r="B35" s="9">
+      <c r="K34" s="20"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="21"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
         <v>12</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="7">
         <v>99</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="12">
         <v>1.5399793559194999E-2</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="10">
         <v>0.78676070623234695</v>
       </c>
-      <c r="G35" s="13">
+      <c r="G35" s="10">
         <v>0.43332043259999797</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="9">
-        <v>9</v>
-      </c>
-      <c r="B36" s="9">
+      <c r="K35" s="22"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="23"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7">
         <v>12</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="7">
         <v>99</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="12">
         <v>4.1963339851818701E-2</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="10">
         <v>1.9830952728584299</v>
       </c>
-      <c r="G36" s="13">
+      <c r="G36" s="10">
         <v>5.0155542116857701E-2</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="9">
-        <v>9</v>
-      </c>
-      <c r="B37" s="9">
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="21"/>
+      <c r="N36" s="21"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>9</v>
+      </c>
+      <c r="B37" s="7">
         <v>12</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="9">
+      <c r="C37" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="7">
         <v>99</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="12">
         <v>2.6563546292623599E-2</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="10">
         <v>1.36957393403213</v>
       </c>
-      <c r="G37" s="13">
+      <c r="G37" s="10">
         <v>0.17395011282650499</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="8">
+      <c r="K37" s="23"/>
+      <c r="L37" s="23"/>
+      <c r="M37" s="23"/>
+      <c r="N37" s="23"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
         <v>12</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="6">
         <v>3</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="6">
         <v>105</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="11">
         <v>-6.2206069450507998E-3</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="9">
         <v>-0.53583211527644603</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="9">
         <v>0.59321870892864503</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8">
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="21"/>
+      <c r="N38" s="21"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
         <v>12</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="6">
         <v>3</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="6">
         <v>105</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="11">
         <v>1.55610672921839E-2</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="9">
         <v>1.7682394061761799</v>
       </c>
-      <c r="G39" s="12">
+      <c r="G39" s="9">
         <v>7.9953173706632505E-2</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
+      <c r="K39" s="23"/>
+      <c r="L39" s="23"/>
+      <c r="M39" s="23"/>
+      <c r="N39" s="23"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
         <v>12</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="5">
         <v>3</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="8">
+      <c r="C40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="6">
         <v>105</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="11">
         <v>2.1781674237234702E-2</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F40" s="9">
         <v>2.18444160507469</v>
       </c>
-      <c r="G40" s="12">
+      <c r="G40" s="9">
         <v>3.1175742226854802E-2</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="9">
+      <c r="K40" s="21"/>
+      <c r="L40" s="21"/>
+      <c r="M40" s="21"/>
+      <c r="N40" s="21"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
         <v>12</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="7">
         <v>6</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="7">
         <v>102</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="12">
         <v>-6.9457633388909999E-4</v>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="10">
         <v>-4.6921789058382297E-2</v>
       </c>
-      <c r="G41" s="13">
+      <c r="G41" s="10">
         <v>0.96266821624608201</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="9">
+      <c r="K41" s="23"/>
+      <c r="L41" s="23"/>
+      <c r="M41" s="23"/>
+      <c r="N41" s="23"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
         <v>12</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="7">
         <v>6</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="7">
         <v>102</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="12">
         <v>2.14332070845108E-2</v>
       </c>
-      <c r="F42" s="13">
+      <c r="F42" s="10">
         <v>1.5868298092322599</v>
       </c>
-      <c r="G42" s="13">
+      <c r="G42" s="10">
         <v>0.11567711128970599</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="9">
+      <c r="K42" s="20"/>
+      <c r="L42" s="21"/>
+      <c r="M42" s="21"/>
+      <c r="N42" s="21"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
         <v>12</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43" s="7">
         <v>6</v>
       </c>
-      <c r="C43" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="9">
+      <c r="C43" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="7">
         <v>102</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="12">
         <v>2.21277834183999E-2</v>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="10">
         <v>1.5686371069098901</v>
       </c>
-      <c r="G43" s="13">
+      <c r="G43" s="10">
         <v>0.119860281551464</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="8">
+      <c r="K43" s="22"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="23"/>
+      <c r="N43" s="23"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
         <v>12</v>
       </c>
-      <c r="B44" s="8">
-        <v>9</v>
-      </c>
-      <c r="C44" s="8" t="s">
+      <c r="B44" s="6">
+        <v>9</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="6">
         <v>99</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="11">
         <v>1.7274350360729E-2</v>
       </c>
-      <c r="F44" s="12">
+      <c r="F44" s="9">
         <v>0.96718798430602604</v>
       </c>
-      <c r="G44" s="12">
+      <c r="G44" s="9">
         <v>0.335830909036957</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="8">
+      <c r="K44" s="20"/>
+      <c r="L44" s="21"/>
+      <c r="M44" s="21"/>
+      <c r="N44" s="21"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
         <v>12</v>
       </c>
-      <c r="B45" s="8">
-        <v>9</v>
-      </c>
-      <c r="C45" s="8" t="s">
+      <c r="B45" s="6">
+        <v>9</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="6">
         <v>99</v>
       </c>
-      <c r="E45" s="14">
+      <c r="E45" s="11">
         <v>3.3700752615642197E-2</v>
       </c>
-      <c r="F45" s="12">
+      <c r="F45" s="9">
         <v>1.9111876517641899</v>
       </c>
-      <c r="G45" s="12">
+      <c r="G45" s="9">
         <v>5.8902534117065301E-2</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="8">
+      <c r="K45" s="22"/>
+      <c r="L45" s="23"/>
+      <c r="M45" s="23"/>
+      <c r="N45" s="23"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
         <v>12</v>
       </c>
-      <c r="B46" s="8">
-        <v>9</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="8">
+      <c r="B46" s="6">
+        <v>9</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="6">
         <v>99</v>
       </c>
-      <c r="E46" s="14">
+      <c r="E46" s="11">
         <v>1.6426402254913201E-2</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="9">
         <v>0.93121947420209605</v>
       </c>
-      <c r="G46" s="12">
+      <c r="G46" s="9">
         <v>0.35402843630614</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="9">
+      <c r="K46" s="20"/>
+      <c r="L46" s="21"/>
+      <c r="M46" s="21"/>
+      <c r="N46" s="21"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
         <v>12</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="7">
         <v>12</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="7">
         <v>96</v>
       </c>
-      <c r="E47" s="15">
+      <c r="E47" s="12">
         <v>4.7582304856785398E-2</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F47" s="10">
         <v>2.1319726491645499</v>
       </c>
-      <c r="G47" s="13">
+      <c r="G47" s="10">
         <v>3.5588701036567499E-2</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="9">
+      <c r="K47" s="22"/>
+      <c r="L47" s="23"/>
+      <c r="M47" s="23"/>
+      <c r="N47" s="23"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
         <v>12</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="7">
         <v>12</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="7">
         <v>96</v>
       </c>
-      <c r="E48" s="15">
+      <c r="E48" s="12">
         <v>5.05347405509049E-2</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F48" s="10">
         <v>2.24675213526971</v>
       </c>
-      <c r="G48" s="13">
+      <c r="G48" s="10">
         <v>2.6971310954366098E-2</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="9">
+      <c r="K48" s="21"/>
+      <c r="L48" s="21"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="21"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
         <v>12</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B49" s="7">
         <v>12</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="9">
+      <c r="C49" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="7">
         <v>96</v>
       </c>
-      <c r="E49" s="15">
+      <c r="E49" s="12">
         <v>2.9524356941194999E-3</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F49" s="10">
         <v>0.12530451887434399</v>
       </c>
-      <c r="G49" s="13">
+      <c r="G49" s="10">
         <v>0.90054726036784105</v>
       </c>
+      <c r="K49" s="23"/>
+      <c r="L49" s="23"/>
+      <c r="M49" s="23"/>
+      <c r="N49" s="23"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K50" s="21"/>
+      <c r="L50" s="21"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="21"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K51" s="23"/>
+      <c r="L51" s="23"/>
+      <c r="M51" s="23"/>
+      <c r="N51" s="23"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="21"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K53" s="23"/>
+      <c r="L53" s="23"/>
+      <c r="M53" s="23"/>
+      <c r="N53" s="23"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K55" s="23"/>
+      <c r="L55" s="23"/>
+      <c r="M55" s="23"/>
+      <c r="N55" s="23"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K56" s="21"/>
+      <c r="L56" s="21"/>
+      <c r="M56" s="21"/>
+      <c r="N56" s="21"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K57" s="23"/>
+      <c r="L57" s="23"/>
+      <c r="M57" s="23"/>
+      <c r="N57" s="23"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K58" s="21"/>
+      <c r="L58" s="21"/>
+      <c r="M58" s="21"/>
+      <c r="N58" s="21"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K59" s="23"/>
+      <c r="L59" s="23"/>
+      <c r="M59" s="23"/>
+      <c r="N59" s="23"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K60" s="24"/>
+      <c r="L60" s="24"/>
+      <c r="M60" s="24"/>
+      <c r="N60" s="24"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G49" xr:uid="{828DFD01-9D50-4EA6-A7DD-A0B766D34BA5}">
@@ -2841,6 +3318,16 @@
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="I18:I23"/>
+    <mergeCell ref="I24:I29"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="I6:I11"/>
+    <mergeCell ref="I12:I17"/>
+  </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">

--- a/data/analysis/momentumNew/mergeTtestResult/merged_t_test.xlsx
+++ b/data/analysis/momentumNew/mergeTtestResult/merged_t_test.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Han\學習\金融策略\分析程式\data\analysis\momentumNew\mergeTtestResult\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B00524-421A-4D13-AA67-B05EDD2B73A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6557CE94-440C-4568-AE55-19E2F958E748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{79B926A8-815C-4ADE-A3A1-103001E1D343}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{79B926A8-815C-4ADE-A3A1-103001E1D343}"/>
   </bookViews>
   <sheets>
     <sheet name="merged_t_test" sheetId="1" r:id="rId1"/>
+    <sheet name="15years" sheetId="2" r:id="rId2"/>
+    <sheet name="improved" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">merged_t_test!$A$1:$G$49</definedName>
@@ -1046,7 +1048,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1106,21 +1108,6 @@
     </xf>
     <xf numFmtId="176" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="21" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1128,6 +1115,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="35" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1143,91 +1211,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="35" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1602,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{828DFD01-9D50-4EA6-A7DD-A0B766D34BA5}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11.375" style="8" customWidth="1"/>
@@ -1706,14 +1690,14 @@
       <c r="G4" s="9">
         <v>5.1106356269530005E-4</v>
       </c>
-      <c r="I4" s="39" t="s">
+      <c r="I4" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="40"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="48"/>
     </row>
     <row r="5" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
@@ -1737,10 +1721,10 @@
       <c r="G5" s="10">
         <v>0.25494625406830401</v>
       </c>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="26" t="s">
+      <c r="J5" s="21" t="s">
         <v>45</v>
       </c>
       <c r="K5" s="15">
@@ -1752,7 +1736,7 @@
       <c r="M5" s="15">
         <v>9</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="29">
         <v>12</v>
       </c>
     </row>
@@ -1778,25 +1762,25 @@
       <c r="G6" s="10">
         <v>7.9232025762956804E-6</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="54">
         <v>3</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J6" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="14">
         <f>$E2</f>
         <v>3.0260421823129999E-4</v>
       </c>
-      <c r="L6" s="21">
+      <c r="L6" s="14">
         <f>$E5</f>
         <v>1.51301049852723E-2</v>
       </c>
-      <c r="M6" s="21">
+      <c r="M6" s="14">
         <f>$E8</f>
         <v>1.51244575442856E-2</v>
       </c>
-      <c r="N6" s="44">
+      <c r="N6" s="30">
         <f>$E11</f>
         <v>2.3280515551955899E-2</v>
       </c>
@@ -1823,21 +1807,21 @@
       <c r="G7" s="10">
         <v>2.184178713642E-4</v>
       </c>
-      <c r="I7" s="45"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="25" t="str">
+      <c r="I7" s="43"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="20" t="str">
         <f>"("&amp;TEXT($F2, "0.00")&amp;")"</f>
         <v>(0.03)</v>
       </c>
-      <c r="L7" s="25" t="str">
+      <c r="L7" s="20" t="str">
         <f>"("&amp;TEXT($F5, "0.00")&amp;")"</f>
         <v>(1.14)</v>
       </c>
-      <c r="M7" s="25" t="str">
+      <c r="M7" s="20" t="str">
         <f>"("&amp;TEXT($F8, "0.00")&amp;")"</f>
         <v>(0.96)</v>
       </c>
-      <c r="N7" s="46" t="str">
+      <c r="N7" s="31" t="str">
         <f>"("&amp;TEXT($F11, "0.00")&amp;")"</f>
         <v>(1.16)</v>
       </c>
@@ -1864,23 +1848,23 @@
       <c r="G8" s="9">
         <v>0.34096046080184</v>
       </c>
-      <c r="I8" s="45"/>
-      <c r="J8" s="29" t="s">
+      <c r="I8" s="43"/>
+      <c r="J8" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="47">
+      <c r="K8" s="32">
         <f>$E3</f>
         <v>3.0722210317410001E-2</v>
       </c>
-      <c r="L8" s="47">
+      <c r="L8" s="32">
         <f>$E6</f>
         <v>6.5631060309720005E-2</v>
       </c>
-      <c r="M8" s="47">
+      <c r="M8" s="32">
         <f>$E9</f>
         <v>9.0526528336692905E-2</v>
       </c>
-      <c r="N8" s="48">
+      <c r="N8" s="33">
         <f>$E12</f>
         <v>9.33097832882889E-2</v>
       </c>
@@ -1907,21 +1891,21 @@
       <c r="G9" s="9">
         <v>1.2141876138480901E-6</v>
       </c>
-      <c r="I9" s="45"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="36" t="str">
+      <c r="I9" s="43"/>
+      <c r="J9" s="50"/>
+      <c r="K9" s="26" t="str">
         <f>"("&amp;TEXT($F3,"0.00")&amp;")"</f>
         <v>(3.55)</v>
       </c>
-      <c r="L9" s="36" t="str">
+      <c r="L9" s="26" t="str">
         <f>"("&amp;TEXT($F6,"0.00")&amp;")"</f>
         <v>(4.69)</v>
       </c>
-      <c r="M9" s="36" t="str">
+      <c r="M9" s="26" t="str">
         <f>"("&amp;TEXT($F9,"0.00")&amp;")"</f>
         <v>(5.15)</v>
       </c>
-      <c r="N9" s="49" t="str">
+      <c r="N9" s="34" t="str">
         <f>"("&amp;TEXT($F12,"0.00")&amp;")"</f>
         <v>(4.41)</v>
       </c>
@@ -1948,23 +1932,23 @@
       <c r="G10" s="9">
         <v>1.7724280876774E-5</v>
       </c>
-      <c r="I10" s="45"/>
-      <c r="J10" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="47">
+      <c r="I10" s="43"/>
+      <c r="J10" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="32">
         <f>$E4</f>
         <v>3.0419606099178698E-2</v>
       </c>
-      <c r="L10" s="47">
+      <c r="L10" s="32">
         <f>$E7</f>
         <v>5.0500955324447698E-2</v>
       </c>
-      <c r="M10" s="47">
+      <c r="M10" s="32">
         <f>$E10</f>
         <v>7.5402070792407294E-2</v>
       </c>
-      <c r="N10" s="48">
+      <c r="N10" s="33">
         <f>$E13</f>
         <v>7.0029267736333001E-2</v>
       </c>
@@ -1991,21 +1975,21 @@
       <c r="G11" s="10">
         <v>0.24789234222405299</v>
       </c>
-      <c r="I11" s="50"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="37" t="str">
+      <c r="I11" s="44"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="27" t="str">
         <f>"("&amp;TEXT($F4,"0.00")&amp;")"</f>
         <v>(3.58)</v>
       </c>
-      <c r="L11" s="37" t="str">
+      <c r="L11" s="27" t="str">
         <f>"("&amp;TEXT($F7,"0.00")&amp;")"</f>
         <v>(3.82)</v>
       </c>
-      <c r="M11" s="37" t="str">
+      <c r="M11" s="27" t="str">
         <f>"("&amp;TEXT($F10,"0.00")&amp;")"</f>
         <v>(4.49)</v>
       </c>
-      <c r="N11" s="51" t="str">
+      <c r="N11" s="35" t="str">
         <f>"("&amp;TEXT($F13,"0.00")&amp;")"</f>
         <v>(3.39)</v>
       </c>
@@ -2032,22 +2016,22 @@
       <c r="G12" s="10">
         <v>2.5034503907783899E-5</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12" s="42">
         <v>6</v>
       </c>
-      <c r="J12" s="32" t="s">
+      <c r="J12" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="K12" s="21">
+      <c r="K12" s="14">
         <v>4.7735012474096001E-3</v>
       </c>
-      <c r="L12" s="21">
+      <c r="L12" s="14">
         <v>1.89783044088855E-2</v>
       </c>
-      <c r="M12" s="21">
+      <c r="M12" s="14">
         <v>1.99711867006667E-2</v>
       </c>
-      <c r="N12" s="44">
+      <c r="N12" s="30">
         <v>3.0649711185840801E-2</v>
       </c>
     </row>
@@ -2073,18 +2057,18 @@
       <c r="G13" s="10">
         <v>9.8533179837500011E-4</v>
       </c>
-      <c r="I13" s="45"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="25" t="s">
+      <c r="I13" s="43"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="L13" s="25" t="s">
+      <c r="L13" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="M13" s="25" t="s">
+      <c r="M13" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="N13" s="46" t="s">
+      <c r="N13" s="31" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2110,20 +2094,20 @@
       <c r="G14" s="9">
         <v>0.65423383389473</v>
       </c>
-      <c r="I14" s="45"/>
-      <c r="J14" s="32" t="s">
+      <c r="I14" s="43"/>
+      <c r="J14" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="47">
+      <c r="K14" s="32">
         <v>2.7115683765055399E-2</v>
       </c>
-      <c r="L14" s="47">
+      <c r="L14" s="32">
         <v>5.4315765000363898E-2</v>
       </c>
-      <c r="M14" s="47">
+      <c r="M14" s="32">
         <v>6.03256929965394E-2</v>
       </c>
-      <c r="N14" s="48">
+      <c r="N14" s="33">
         <v>5.3065850483251402E-2</v>
       </c>
     </row>
@@ -2149,18 +2133,18 @@
       <c r="G15" s="9">
         <v>2.1961835765053998E-3</v>
       </c>
-      <c r="I15" s="45"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="36" t="s">
+      <c r="I15" s="43"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="L15" s="36" t="s">
+      <c r="L15" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="36" t="s">
+      <c r="M15" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="N15" s="49" t="s">
+      <c r="N15" s="34" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2186,20 +2170,20 @@
       <c r="G16" s="9">
         <v>8.3279350537053005E-3</v>
       </c>
-      <c r="I16" s="45"/>
-      <c r="J16" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="47">
+      <c r="I16" s="43"/>
+      <c r="J16" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="32">
         <v>2.23421825176458E-2</v>
       </c>
-      <c r="L16" s="47">
+      <c r="L16" s="32">
         <v>3.5337460591478298E-2</v>
       </c>
-      <c r="M16" s="47">
+      <c r="M16" s="32">
         <v>4.0354506295872603E-2</v>
       </c>
-      <c r="N16" s="44">
+      <c r="N16" s="30">
         <v>2.2416139297410601E-2</v>
       </c>
     </row>
@@ -2225,18 +2209,18 @@
       <c r="G17" s="10">
         <v>0.18067514945157101</v>
       </c>
-      <c r="I17" s="50"/>
-      <c r="J17" s="35"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="25"/>
       <c r="K17" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="L17" s="37" t="s">
+      <c r="L17" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="M17" s="37" t="s">
+      <c r="M17" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="N17" s="53" t="s">
+      <c r="N17" s="36" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2262,22 +2246,22 @@
       <c r="G18" s="10">
         <v>6.0419980721123302E-5</v>
       </c>
-      <c r="I18" s="52">
-        <v>9</v>
-      </c>
-      <c r="J18" s="32" t="s">
+      <c r="I18" s="42">
+        <v>9</v>
+      </c>
+      <c r="J18" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="K18" s="21">
+      <c r="K18" s="14">
         <v>5.9719290995810005E-4</v>
       </c>
-      <c r="L18" s="21">
+      <c r="L18" s="14">
         <v>6.1873933427599999E-4</v>
       </c>
-      <c r="M18" s="21">
+      <c r="M18" s="14">
         <v>1.523367447362E-3</v>
       </c>
-      <c r="N18" s="44">
+      <c r="N18" s="30">
         <v>1.5399793559194999E-2</v>
       </c>
     </row>
@@ -2303,18 +2287,18 @@
       <c r="G19" s="10">
         <v>3.5367985366198001E-3</v>
       </c>
-      <c r="I19" s="45"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="25" t="s">
+      <c r="I19" s="43"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="L19" s="25" t="s">
+      <c r="L19" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="M19" s="25" t="s">
+      <c r="M19" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="N19" s="46" t="s">
+      <c r="N19" s="31" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2340,20 +2324,20 @@
       <c r="G20" s="9">
         <v>0.231100321207518</v>
       </c>
-      <c r="I20" s="45"/>
-      <c r="J20" s="32" t="s">
+      <c r="I20" s="43"/>
+      <c r="J20" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="47">
+      <c r="K20" s="32">
         <v>2.8474975298435901E-2</v>
       </c>
-      <c r="L20" s="47">
+      <c r="L20" s="32">
         <v>4.1623593254200397E-2</v>
       </c>
-      <c r="M20" s="47">
+      <c r="M20" s="32">
         <v>4.0294606718451698E-2</v>
       </c>
-      <c r="N20" s="48">
+      <c r="N20" s="33">
         <v>4.1963339851818701E-2</v>
       </c>
     </row>
@@ -2379,18 +2363,18 @@
       <c r="G21" s="9">
         <v>4.7856639655370002E-4</v>
       </c>
-      <c r="I21" s="45"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="36" t="s">
+      <c r="I21" s="43"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="L21" s="36" t="s">
+      <c r="L21" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="M21" s="36" t="s">
+      <c r="M21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="N21" s="49" t="s">
+      <c r="N21" s="34" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2416,20 +2400,20 @@
       <c r="G22" s="9">
         <v>7.9506872459265999E-3</v>
       </c>
-      <c r="I22" s="45"/>
-      <c r="J22" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="47">
+      <c r="I22" s="43"/>
+      <c r="J22" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="32">
         <v>2.7877782388477702E-2</v>
       </c>
-      <c r="L22" s="47">
+      <c r="L22" s="32">
         <v>4.1004853919924297E-2</v>
       </c>
-      <c r="M22" s="47">
+      <c r="M22" s="32">
         <v>3.8771239271089601E-2</v>
       </c>
-      <c r="N22" s="44">
+      <c r="N22" s="30">
         <v>2.6563546292623599E-2</v>
       </c>
     </row>
@@ -2455,18 +2439,18 @@
       <c r="G23" s="10">
         <v>0.12891208974354801</v>
       </c>
-      <c r="I23" s="50"/>
-      <c r="J23" s="35"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="25"/>
       <c r="K23" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="L23" s="37" t="s">
+      <c r="L23" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="M23" s="37" t="s">
+      <c r="M23" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="N23" s="53" t="s">
+      <c r="N23" s="36" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2492,22 +2476,22 @@
       <c r="G24" s="10">
         <v>8.7196464352812999E-3</v>
       </c>
-      <c r="I24" s="52">
+      <c r="I24" s="42">
         <v>12</v>
       </c>
-      <c r="J24" s="32" t="s">
+      <c r="J24" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="K24" s="21">
+      <c r="K24" s="14">
         <v>-6.2206069450507998E-3</v>
       </c>
-      <c r="L24" s="21">
+      <c r="L24" s="14">
         <v>-6.9457633388909999E-4</v>
       </c>
-      <c r="M24" s="21">
+      <c r="M24" s="14">
         <v>1.7274350360729E-2</v>
       </c>
-      <c r="N24" s="48">
+      <c r="N24" s="33">
         <v>4.7582304856785398E-2</v>
       </c>
     </row>
@@ -2533,18 +2517,18 @@
       <c r="G25" s="10">
         <v>0.208888402471089</v>
       </c>
-      <c r="I25" s="45"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="25" t="s">
+      <c r="I25" s="43"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="L25" s="25" t="s">
+      <c r="L25" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="M25" s="25" t="s">
+      <c r="M25" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="N25" s="54" t="s">
+      <c r="N25" s="37" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2570,20 +2554,20 @@
       <c r="G26" s="9">
         <v>0.95805729432186704</v>
       </c>
-      <c r="I26" s="45"/>
-      <c r="J26" s="32" t="s">
+      <c r="I26" s="43"/>
+      <c r="J26" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="21">
+      <c r="K26" s="14">
         <v>1.55610672921839E-2</v>
       </c>
-      <c r="L26" s="21">
+      <c r="L26" s="14">
         <v>2.14332070845108E-2</v>
       </c>
-      <c r="M26" s="21">
+      <c r="M26" s="14">
         <v>3.3700752615642197E-2</v>
       </c>
-      <c r="N26" s="48">
+      <c r="N26" s="33">
         <v>5.05347405509049E-2</v>
       </c>
     </row>
@@ -2609,18 +2593,18 @@
       <c r="G27" s="9">
         <v>1.6370331429953E-3</v>
       </c>
-      <c r="I27" s="45"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="25" t="s">
+      <c r="I27" s="43"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="L27" s="25" t="s">
+      <c r="L27" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="M27" s="25" t="s">
+      <c r="M27" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="N27" s="54" t="s">
+      <c r="N27" s="37" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2646,20 +2630,20 @@
       <c r="G28" s="9">
         <v>4.6583346619845003E-3</v>
       </c>
-      <c r="I28" s="45"/>
-      <c r="J28" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="K28" s="47">
+      <c r="I28" s="43"/>
+      <c r="J28" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="32">
         <v>2.1781674237234702E-2</v>
       </c>
-      <c r="L28" s="60">
+      <c r="L28" s="14">
         <v>2.21277834183999E-2</v>
       </c>
-      <c r="M28" s="60">
+      <c r="M28" s="14">
         <v>1.6426402254913201E-2</v>
       </c>
-      <c r="N28" s="44">
+      <c r="N28" s="30">
         <v>2.9524356941194999E-3</v>
       </c>
     </row>
@@ -2685,18 +2669,18 @@
       <c r="G29" s="10">
         <v>0.96471301456515401</v>
       </c>
-      <c r="I29" s="55"/>
-      <c r="J29" s="56"/>
-      <c r="K29" s="57" t="s">
+      <c r="I29" s="45"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="L29" s="58" t="s">
+      <c r="L29" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="M29" s="58" t="s">
+      <c r="M29" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="N29" s="59" t="s">
+      <c r="N29" s="41" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2830,10 +2814,10 @@
       <c r="G34" s="9">
         <v>1.4720291072391501E-2</v>
       </c>
-      <c r="K34" s="20"/>
-      <c r="L34" s="21"/>
-      <c r="M34" s="21"/>
-      <c r="N34" s="21"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
@@ -2857,10 +2841,10 @@
       <c r="G35" s="10">
         <v>0.43332043259999797</v>
       </c>
-      <c r="K35" s="22"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="23"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
@@ -2884,10 +2868,10 @@
       <c r="G36" s="10">
         <v>5.0155542116857701E-2</v>
       </c>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="21"/>
-      <c r="N36" s="21"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
@@ -2911,10 +2895,10 @@
       <c r="G37" s="10">
         <v>0.17395011282650499</v>
       </c>
-      <c r="K37" s="23"/>
-      <c r="L37" s="23"/>
-      <c r="M37" s="23"/>
-      <c r="N37" s="23"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
@@ -2938,10 +2922,10 @@
       <c r="G38" s="9">
         <v>0.59321870892864503</v>
       </c>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="21"/>
-      <c r="N38" s="21"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
@@ -2965,10 +2949,10 @@
       <c r="G39" s="9">
         <v>7.9953173706632505E-2</v>
       </c>
-      <c r="K39" s="23"/>
-      <c r="L39" s="23"/>
-      <c r="M39" s="23"/>
-      <c r="N39" s="23"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
@@ -2992,10 +2976,10 @@
       <c r="G40" s="9">
         <v>3.1175742226854802E-2</v>
       </c>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
-      <c r="N40" s="21"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
@@ -3019,10 +3003,10 @@
       <c r="G41" s="10">
         <v>0.96266821624608201</v>
       </c>
-      <c r="K41" s="23"/>
-      <c r="L41" s="23"/>
-      <c r="M41" s="23"/>
-      <c r="N41" s="23"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="16"/>
+      <c r="N41" s="16"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
@@ -3046,10 +3030,10 @@
       <c r="G42" s="10">
         <v>0.11567711128970599</v>
       </c>
-      <c r="K42" s="20"/>
-      <c r="L42" s="21"/>
-      <c r="M42" s="21"/>
-      <c r="N42" s="21"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
@@ -3073,10 +3057,10 @@
       <c r="G43" s="10">
         <v>0.119860281551464</v>
       </c>
-      <c r="K43" s="22"/>
-      <c r="L43" s="23"/>
-      <c r="M43" s="23"/>
-      <c r="N43" s="23"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="16"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
@@ -3100,10 +3084,10 @@
       <c r="G44" s="9">
         <v>0.335830909036957</v>
       </c>
-      <c r="K44" s="20"/>
-      <c r="L44" s="21"/>
-      <c r="M44" s="21"/>
-      <c r="N44" s="21"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="14"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="14"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -3127,10 +3111,10 @@
       <c r="G45" s="9">
         <v>5.8902534117065301E-2</v>
       </c>
-      <c r="K45" s="22"/>
-      <c r="L45" s="23"/>
-      <c r="M45" s="23"/>
-      <c r="N45" s="23"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -3154,10 +3138,10 @@
       <c r="G46" s="9">
         <v>0.35402843630614</v>
       </c>
-      <c r="K46" s="20"/>
-      <c r="L46" s="21"/>
-      <c r="M46" s="21"/>
-      <c r="N46" s="21"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="14"/>
+      <c r="M46" s="14"/>
+      <c r="N46" s="14"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
@@ -3181,10 +3165,10 @@
       <c r="G47" s="10">
         <v>3.5588701036567499E-2</v>
       </c>
-      <c r="K47" s="22"/>
-      <c r="L47" s="23"/>
-      <c r="M47" s="23"/>
-      <c r="N47" s="23"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
+      <c r="N47" s="16"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
@@ -3208,10 +3192,10 @@
       <c r="G48" s="10">
         <v>2.6971310954366098E-2</v>
       </c>
-      <c r="K48" s="21"/>
-      <c r="L48" s="21"/>
-      <c r="M48" s="21"/>
-      <c r="N48" s="21"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="14"/>
+      <c r="M48" s="14"/>
+      <c r="N48" s="14"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
@@ -3235,82 +3219,70 @@
       <c r="G49" s="10">
         <v>0.90054726036784105</v>
       </c>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="23"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
+      <c r="N49" s="16"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K50" s="21"/>
-      <c r="L50" s="21"/>
-      <c r="M50" s="21"/>
-      <c r="N50" s="21"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="14"/>
+      <c r="M50" s="14"/>
+      <c r="N50" s="14"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K51" s="23"/>
-      <c r="L51" s="23"/>
-      <c r="M51" s="23"/>
-      <c r="N51" s="23"/>
+      <c r="K51" s="16"/>
+      <c r="L51" s="16"/>
+      <c r="M51" s="16"/>
+      <c r="N51" s="16"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K52" s="21"/>
-      <c r="L52" s="21"/>
-      <c r="M52" s="21"/>
-      <c r="N52" s="21"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="14"/>
+      <c r="M52" s="14"/>
+      <c r="N52" s="14"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K53" s="23"/>
-      <c r="L53" s="23"/>
-      <c r="M53" s="23"/>
-      <c r="N53" s="23"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
+      <c r="N53" s="16"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K54" s="21"/>
-      <c r="L54" s="21"/>
-      <c r="M54" s="21"/>
-      <c r="N54" s="21"/>
+      <c r="K54" s="14"/>
+      <c r="L54" s="14"/>
+      <c r="M54" s="14"/>
+      <c r="N54" s="14"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K55" s="23"/>
-      <c r="L55" s="23"/>
-      <c r="M55" s="23"/>
-      <c r="N55" s="23"/>
+      <c r="K55" s="16"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
+      <c r="N55" s="16"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K56" s="21"/>
-      <c r="L56" s="21"/>
-      <c r="M56" s="21"/>
-      <c r="N56" s="21"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="14"/>
+      <c r="N56" s="14"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K57" s="23"/>
-      <c r="L57" s="23"/>
-      <c r="M57" s="23"/>
-      <c r="N57" s="23"/>
+      <c r="K57" s="16"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="16"/>
+      <c r="N57" s="16"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K58" s="21"/>
-      <c r="L58" s="21"/>
-      <c r="M58" s="21"/>
-      <c r="N58" s="21"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="14"/>
+      <c r="M58" s="14"/>
+      <c r="N58" s="14"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K59" s="23"/>
-      <c r="L59" s="23"/>
-      <c r="M59" s="23"/>
-      <c r="N59" s="23"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K60" s="24"/>
-      <c r="L60" s="24"/>
-      <c r="M60" s="24"/>
-      <c r="N60" s="24"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
+      <c r="K59" s="16"/>
+      <c r="L59" s="16"/>
+      <c r="M59" s="16"/>
+      <c r="N59" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G49" xr:uid="{828DFD01-9D50-4EA6-A7DD-A0B766D34BA5}">
@@ -3345,4 +3317,24 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60641E96-17E1-4C28-95A7-3B3EADA10A6C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA12766-CA57-4195-AB5D-D953190D2612}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/analysis/momentumNew/mergeTtestResult/merged_t_test.xlsx
+++ b/data/analysis/momentumNew/mergeTtestResult/merged_t_test.xlsx
@@ -8,24 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Han\學習\金融策略\分析程式\data\analysis\momentumNew\mergeTtestResult\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6557CE94-440C-4568-AE55-19E2F958E748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C463C36D-CFEB-4182-8491-035EBF9B57C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{79B926A8-815C-4ADE-A3A1-103001E1D343}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{79B926A8-815C-4ADE-A3A1-103001E1D343}"/>
   </bookViews>
   <sheets>
-    <sheet name="merged_t_test" sheetId="1" r:id="rId1"/>
-    <sheet name="15years" sheetId="2" r:id="rId2"/>
-    <sheet name="improved" sheetId="3" r:id="rId3"/>
+    <sheet name="mv150_10years" sheetId="1" r:id="rId1"/>
+    <sheet name="mv150_15years" sheetId="2" r:id="rId2"/>
+    <sheet name="priceOver10" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">merged_t_test!$A$1:$G$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mv150_10years!$A$2:$G$50</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="50">
   <si>
     <t>remark</t>
   </si>
@@ -173,6 +173,14 @@
     <t>Panel A</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
+  <si>
+    <t>2010~2019</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010~2024</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -181,7 +189,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -374,8 +382,14 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -573,8 +587,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="31">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -916,6 +936,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1048,7 +1131,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1115,18 +1198,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="22" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1163,55 +1234,124 @@
     <xf numFmtId="176" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1260,7 +1400,112 @@
     <cellStyle name="壞" xfId="8" builtinId="27" customBuiltin="1"/>
     <cellStyle name="警告文字" xfId="15" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1586,7 +1831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{828DFD01-9D50-4EA6-A7DD-A0B766D34BA5}">
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11.375" style="8" customWidth="1"/>
@@ -1599,50 +1844,38 @@
     <col min="11" max="14" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="F2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>3</v>
-      </c>
-      <c r="B2" s="6">
-        <v>3</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="6">
-        <v>114</v>
-      </c>
-      <c r="E2" s="11">
-        <v>3.0260421823129999E-4</v>
-      </c>
-      <c r="F2" s="9">
-        <v>2.8355084394913299E-2</v>
-      </c>
-      <c r="G2" s="9">
-        <v>0.97742896460482598</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1653,220 +1886,200 @@
         <v>3</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="6">
         <v>114</v>
       </c>
       <c r="E3" s="11">
-        <v>3.0722210317410001E-2</v>
+        <v>3.0260421823129999E-4</v>
       </c>
       <c r="F3" s="9">
-        <v>3.54698888875836</v>
+        <v>2.8355084394913299E-2</v>
       </c>
       <c r="G3" s="9">
-        <v>5.6845064904419997E-4</v>
+        <v>0.97742896460482598</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6">
         <v>3</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="6">
         <v>114</v>
       </c>
       <c r="E4" s="11">
+        <v>3.0722210317410001E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>3.54698888875836</v>
+      </c>
+      <c r="G4" s="9">
+        <v>5.6845064904419997E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="6">
+        <v>114</v>
+      </c>
+      <c r="E5" s="11">
         <v>3.0419606099178698E-2</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F5" s="9">
         <v>3.5780818191419801</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G5" s="9">
         <v>5.1106356269530005E-4</v>
       </c>
-      <c r="I4" s="46" t="s">
+      <c r="I5" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="48"/>
-    </row>
-    <row r="5" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>6</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="43"/>
+    </row>
+    <row r="6" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="D5" s="7">
-        <v>111</v>
-      </c>
-      <c r="E5" s="12">
-        <v>1.51301049852723E-2</v>
-      </c>
-      <c r="F5" s="10">
-        <v>1.1443893939324601</v>
-      </c>
-      <c r="G5" s="10">
-        <v>0.25494625406830401</v>
-      </c>
-      <c r="I5" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="15">
-        <v>3</v>
-      </c>
-      <c r="L5" s="15">
-        <v>6</v>
-      </c>
-      <c r="M5" s="15">
-        <v>9</v>
-      </c>
-      <c r="N5" s="29">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7">
-        <v>6</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="D6" s="7">
         <v>111</v>
       </c>
       <c r="E6" s="12">
-        <v>6.5631060309720005E-2</v>
+        <v>1.51301049852723E-2</v>
       </c>
       <c r="F6" s="10">
-        <v>4.6891959760591497</v>
+        <v>1.1443893939324601</v>
       </c>
       <c r="G6" s="10">
-        <v>7.9232025762956804E-6</v>
-      </c>
-      <c r="I6" s="54">
-        <v>3</v>
-      </c>
-      <c r="J6" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="14">
-        <f>$E2</f>
-        <v>3.0260421823129999E-4</v>
-      </c>
-      <c r="L6" s="14">
-        <f>$E5</f>
-        <v>1.51301049852723E-2</v>
-      </c>
-      <c r="M6" s="14">
-        <f>$E8</f>
-        <v>1.51244575442856E-2</v>
-      </c>
-      <c r="N6" s="30">
-        <f>$E11</f>
-        <v>2.3280515551955899E-2</v>
+        <v>0.25494625406830401</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="15">
+        <v>3</v>
+      </c>
+      <c r="L6" s="15">
+        <v>6</v>
+      </c>
+      <c r="M6" s="15">
+        <v>9</v>
+      </c>
+      <c r="N6" s="25">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="A7" s="7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7">
         <v>6</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="7">
         <v>111</v>
       </c>
       <c r="E7" s="12">
+        <v>6.5631060309720005E-2</v>
+      </c>
+      <c r="F7" s="10">
+        <v>4.6891959760591497</v>
+      </c>
+      <c r="G7" s="10">
+        <v>7.9232025762956804E-6</v>
+      </c>
+      <c r="I7" s="49">
+        <v>3</v>
+      </c>
+      <c r="J7" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="14">
+        <f>$E3</f>
+        <v>3.0260421823129999E-4</v>
+      </c>
+      <c r="L7" s="14">
+        <f>$E6</f>
+        <v>1.51301049852723E-2</v>
+      </c>
+      <c r="M7" s="14">
+        <f>$E9</f>
+        <v>1.51244575442856E-2</v>
+      </c>
+      <c r="N7" s="26">
+        <f>$E12</f>
+        <v>2.3280515551955899E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="7">
+        <v>111</v>
+      </c>
+      <c r="E8" s="12">
         <v>5.0500955324447698E-2</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F8" s="10">
         <v>3.8236782043989401</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G8" s="10">
         <v>2.184178713642E-4</v>
       </c>
-      <c r="I7" s="43"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="20" t="str">
-        <f>"("&amp;TEXT($F2, "0.00")&amp;")"</f>
+      <c r="I8" s="38"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="20" t="str">
+        <f>"("&amp;TEXT($F3, "0.00")&amp;")"</f>
         <v>(0.03)</v>
       </c>
-      <c r="L7" s="20" t="str">
-        <f>"("&amp;TEXT($F5, "0.00")&amp;")"</f>
+      <c r="L8" s="20" t="str">
+        <f>"("&amp;TEXT($F6, "0.00")&amp;")"</f>
         <v>(1.14)</v>
       </c>
-      <c r="M7" s="20" t="str">
-        <f>"("&amp;TEXT($F8, "0.00")&amp;")"</f>
+      <c r="M8" s="20" t="str">
+        <f>"("&amp;TEXT($F9, "0.00")&amp;")"</f>
         <v>(0.96)</v>
       </c>
-      <c r="N7" s="31" t="str">
-        <f>"("&amp;TEXT($F11, "0.00")&amp;")"</f>
+      <c r="N8" s="27" t="str">
+        <f>"("&amp;TEXT($F12, "0.00")&amp;")"</f>
         <v>(1.16)</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>3</v>
-      </c>
-      <c r="B8" s="6">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="6">
-        <v>108</v>
-      </c>
-      <c r="E8" s="11">
-        <v>1.51244575442856E-2</v>
-      </c>
-      <c r="F8" s="9">
-        <v>0.95653052500906299</v>
-      </c>
-      <c r="G8" s="9">
-        <v>0.34096046080184</v>
-      </c>
-      <c r="I8" s="43"/>
-      <c r="J8" s="51" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="32">
-        <f>$E3</f>
-        <v>3.0722210317410001E-2</v>
-      </c>
-      <c r="L8" s="32">
-        <f>$E6</f>
-        <v>6.5631060309720005E-2</v>
-      </c>
-      <c r="M8" s="32">
-        <f>$E9</f>
-        <v>9.0526528336692905E-2</v>
-      </c>
-      <c r="N8" s="33">
-        <f>$E12</f>
-        <v>9.33097832882889E-2</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1877,121 +2090,123 @@
         <v>9</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="6">
         <v>108</v>
       </c>
       <c r="E9" s="11">
+        <v>1.51244575442856E-2</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0.95653052500906299</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0.34096046080184</v>
+      </c>
+      <c r="I9" s="38"/>
+      <c r="J9" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="28">
+        <f>$E4</f>
+        <v>3.0722210317410001E-2</v>
+      </c>
+      <c r="L9" s="28">
+        <f>$E7</f>
+        <v>6.5631060309720005E-2</v>
+      </c>
+      <c r="M9" s="28">
+        <f>$E10</f>
         <v>9.0526528336692905E-2</v>
       </c>
-      <c r="F9" s="9">
-        <v>5.1462038766068803</v>
-      </c>
-      <c r="G9" s="9">
-        <v>1.2141876138480901E-6</v>
-      </c>
-      <c r="I9" s="43"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="26" t="str">
-        <f>"("&amp;TEXT($F3,"0.00")&amp;")"</f>
-        <v>(3.55)</v>
-      </c>
-      <c r="L9" s="26" t="str">
-        <f>"("&amp;TEXT($F6,"0.00")&amp;")"</f>
-        <v>(4.69)</v>
-      </c>
-      <c r="M9" s="26" t="str">
-        <f>"("&amp;TEXT($F9,"0.00")&amp;")"</f>
-        <v>(5.15)</v>
-      </c>
-      <c r="N9" s="34" t="str">
-        <f>"("&amp;TEXT($F12,"0.00")&amp;")"</f>
-        <v>(4.41)</v>
+      <c r="N9" s="29">
+        <f>$E13</f>
+        <v>9.33097832882889E-2</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <v>3</v>
-      </c>
-      <c r="B10" s="5">
+      <c r="A10" s="6">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6">
         <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="6">
         <v>108</v>
       </c>
       <c r="E10" s="11">
+        <v>9.0526528336692905E-2</v>
+      </c>
+      <c r="F10" s="9">
+        <v>5.1462038766068803</v>
+      </c>
+      <c r="G10" s="9">
+        <v>1.2141876138480901E-6</v>
+      </c>
+      <c r="I10" s="38"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="22" t="str">
+        <f>"("&amp;TEXT($F4,"0.00")&amp;")"</f>
+        <v>(3.55)</v>
+      </c>
+      <c r="L10" s="22" t="str">
+        <f>"("&amp;TEXT($F7,"0.00")&amp;")"</f>
+        <v>(4.69)</v>
+      </c>
+      <c r="M10" s="22" t="str">
+        <f>"("&amp;TEXT($F10,"0.00")&amp;")"</f>
+        <v>(5.15)</v>
+      </c>
+      <c r="N10" s="30" t="str">
+        <f>"("&amp;TEXT($F13,"0.00")&amp;")"</f>
+        <v>(4.41)</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="6">
+        <v>108</v>
+      </c>
+      <c r="E11" s="11">
         <v>7.5402070792407294E-2</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F11" s="9">
         <v>4.4945377822361303</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G11" s="9">
         <v>1.7724280876774E-5</v>
       </c>
-      <c r="I10" s="43"/>
-      <c r="J10" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="32">
-        <f>$E4</f>
+      <c r="I11" s="38"/>
+      <c r="J11" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="28">
+        <f>$E5</f>
         <v>3.0419606099178698E-2</v>
       </c>
-      <c r="L10" s="32">
-        <f>$E7</f>
+      <c r="L11" s="28">
+        <f>$E8</f>
         <v>5.0500955324447698E-2</v>
       </c>
-      <c r="M10" s="32">
-        <f>$E10</f>
+      <c r="M11" s="28">
+        <f>$E11</f>
         <v>7.5402070792407294E-2</v>
       </c>
-      <c r="N10" s="33">
-        <f>$E13</f>
+      <c r="N11" s="29">
+        <f>$E14</f>
         <v>7.0029267736333001E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>3</v>
-      </c>
-      <c r="B11" s="7">
-        <v>12</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="7">
-        <v>105</v>
-      </c>
-      <c r="E11" s="12">
-        <v>2.3280515551955899E-2</v>
-      </c>
-      <c r="F11" s="10">
-        <v>1.1620071159640999</v>
-      </c>
-      <c r="G11" s="10">
-        <v>0.24789234222405299</v>
-      </c>
-      <c r="I11" s="44"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="27" t="str">
-        <f>"("&amp;TEXT($F4,"0.00")&amp;")"</f>
-        <v>(3.58)</v>
-      </c>
-      <c r="L11" s="27" t="str">
-        <f>"("&amp;TEXT($F7,"0.00")&amp;")"</f>
-        <v>(3.82)</v>
-      </c>
-      <c r="M11" s="27" t="str">
-        <f>"("&amp;TEXT($F10,"0.00")&amp;")"</f>
-        <v>(4.49)</v>
-      </c>
-      <c r="N11" s="35" t="str">
-        <f>"("&amp;TEXT($F13,"0.00")&amp;")"</f>
-        <v>(3.39)</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2002,113 +2217,115 @@
         <v>12</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12" s="7">
         <v>105</v>
       </c>
       <c r="E12" s="12">
-        <v>9.33097832882889E-2</v>
+        <v>2.3280515551955899E-2</v>
       </c>
       <c r="F12" s="10">
-        <v>4.4123635783784998</v>
+        <v>1.1620071159640999</v>
       </c>
       <c r="G12" s="10">
-        <v>2.5034503907783899E-5</v>
-      </c>
-      <c r="I12" s="42">
-        <v>6</v>
-      </c>
-      <c r="J12" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K12" s="14">
-        <v>4.7735012474096001E-3</v>
-      </c>
-      <c r="L12" s="14">
-        <v>1.89783044088855E-2</v>
-      </c>
-      <c r="M12" s="14">
-        <v>1.99711867006667E-2</v>
-      </c>
-      <c r="N12" s="30">
-        <v>3.0649711185840801E-2</v>
+        <v>0.24789234222405299</v>
+      </c>
+      <c r="I12" s="39"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="23" t="str">
+        <f>"("&amp;TEXT($F5,"0.00")&amp;")"</f>
+        <v>(3.58)</v>
+      </c>
+      <c r="L12" s="23" t="str">
+        <f>"("&amp;TEXT($F8,"0.00")&amp;")"</f>
+        <v>(3.82)</v>
+      </c>
+      <c r="M12" s="23" t="str">
+        <f>"("&amp;TEXT($F11,"0.00")&amp;")"</f>
+        <v>(4.49)</v>
+      </c>
+      <c r="N12" s="31" t="str">
+        <f>"("&amp;TEXT($F14,"0.00")&amp;")"</f>
+        <v>(3.39)</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>3</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="A13" s="7">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7">
         <v>12</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="7">
         <v>105</v>
       </c>
       <c r="E13" s="12">
+        <v>9.33097832882889E-2</v>
+      </c>
+      <c r="F13" s="10">
+        <v>4.4123635783784998</v>
+      </c>
+      <c r="G13" s="10">
+        <v>2.5034503907783899E-5</v>
+      </c>
+      <c r="I13" s="37">
+        <v>6</v>
+      </c>
+      <c r="J13" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="K13" s="14">
+        <v>4.7735012474096001E-3</v>
+      </c>
+      <c r="L13" s="14">
+        <v>1.89783044088855E-2</v>
+      </c>
+      <c r="M13" s="14">
+        <v>1.99711867006667E-2</v>
+      </c>
+      <c r="N13" s="26">
+        <v>3.0649711185840801E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2">
+        <v>12</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="7">
+        <v>105</v>
+      </c>
+      <c r="E14" s="12">
         <v>7.0029267736333001E-2</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F14" s="10">
         <v>3.3910500846225302</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G14" s="10">
         <v>9.8533179837500011E-4</v>
       </c>
-      <c r="I13" s="43"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="20" t="s">
+      <c r="I14" s="38"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="L13" s="20" t="s">
+      <c r="L14" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="M13" s="20" t="s">
+      <c r="M14" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="N13" s="31" t="s">
+      <c r="N14" s="27" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
-        <v>6</v>
-      </c>
-      <c r="B14" s="6">
-        <v>3</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="6">
-        <v>111</v>
-      </c>
-      <c r="E14" s="11">
-        <v>4.7735012474096001E-3</v>
-      </c>
-      <c r="F14" s="9">
-        <v>0.44911286122773603</v>
-      </c>
-      <c r="G14" s="9">
-        <v>0.65423383389473</v>
-      </c>
-      <c r="I14" s="43"/>
-      <c r="J14" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="32">
-        <v>2.7115683765055399E-2</v>
-      </c>
-      <c r="L14" s="32">
-        <v>5.4315765000363898E-2</v>
-      </c>
-      <c r="M14" s="32">
-        <v>6.03256929965394E-2</v>
-      </c>
-      <c r="N14" s="33">
-        <v>5.3065850483251402E-2</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -2119,109 +2336,111 @@
         <v>3</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" s="6">
         <v>111</v>
       </c>
       <c r="E15" s="11">
+        <v>4.7735012474096001E-3</v>
+      </c>
+      <c r="F15" s="9">
+        <v>0.44911286122773603</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0.65423383389473</v>
+      </c>
+      <c r="I15" s="38"/>
+      <c r="J15" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="28">
         <v>2.7115683765055399E-2</v>
       </c>
-      <c r="F15" s="9">
-        <v>3.13615113483938</v>
-      </c>
-      <c r="G15" s="9">
-        <v>2.1961835765053998E-3</v>
-      </c>
-      <c r="I15" s="43"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="L15" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="N15" s="34" t="s">
-        <v>26</v>
+      <c r="L15" s="28">
+        <v>5.4315765000363898E-2</v>
+      </c>
+      <c r="M15" s="28">
+        <v>6.03256929965394E-2</v>
+      </c>
+      <c r="N15" s="29">
+        <v>5.3065850483251402E-2</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <v>6</v>
-      </c>
-      <c r="B16" s="5">
+      <c r="A16" s="6">
+        <v>6</v>
+      </c>
+      <c r="B16" s="6">
         <v>3</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="6">
         <v>111</v>
       </c>
       <c r="E16" s="11">
+        <v>2.7115683765055399E-2</v>
+      </c>
+      <c r="F16" s="9">
+        <v>3.13615113483938</v>
+      </c>
+      <c r="G16" s="9">
+        <v>2.1961835765053998E-3</v>
+      </c>
+      <c r="I16" s="38"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" s="30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>6</v>
+      </c>
+      <c r="B17" s="5">
+        <v>3</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="6">
+        <v>111</v>
+      </c>
+      <c r="E17" s="11">
         <v>2.23421825176458E-2</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F17" s="9">
         <v>2.6870396316370502</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G17" s="9">
         <v>8.3279350537053005E-3</v>
       </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="32">
+      <c r="I17" s="38"/>
+      <c r="J17" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="28">
         <v>2.23421825176458E-2</v>
       </c>
-      <c r="L16" s="32">
+      <c r="L17" s="28">
         <v>3.5337460591478298E-2</v>
       </c>
-      <c r="M16" s="32">
+      <c r="M17" s="28">
         <v>4.0354506295872603E-2</v>
       </c>
-      <c r="N16" s="30">
+      <c r="N17" s="26">
         <v>2.2416139297410601E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>6</v>
-      </c>
-      <c r="B17" s="7">
-        <v>6</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="7">
-        <v>108</v>
-      </c>
-      <c r="E17" s="12">
-        <v>1.89783044088855E-2</v>
-      </c>
-      <c r="F17" s="10">
-        <v>1.34747042886984</v>
-      </c>
-      <c r="G17" s="10">
-        <v>0.18067514945157101</v>
-      </c>
-      <c r="I17" s="44"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="L17" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="N17" s="36" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -2232,113 +2451,111 @@
         <v>6</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" s="7">
         <v>108</v>
       </c>
       <c r="E18" s="12">
-        <v>5.4315765000363898E-2</v>
+        <v>1.89783044088855E-2</v>
       </c>
       <c r="F18" s="10">
-        <v>4.1771525637975904</v>
+        <v>1.34747042886984</v>
       </c>
       <c r="G18" s="10">
-        <v>6.0419980721123302E-5</v>
-      </c>
-      <c r="I18" s="42">
-        <v>9</v>
-      </c>
-      <c r="J18" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K18" s="14">
-        <v>5.9719290995810005E-4</v>
-      </c>
-      <c r="L18" s="14">
-        <v>6.1873933427599999E-4</v>
-      </c>
-      <c r="M18" s="14">
-        <v>1.523367447362E-3</v>
-      </c>
-      <c r="N18" s="30">
-        <v>1.5399793559194999E-2</v>
+        <v>0.18067514945157101</v>
+      </c>
+      <c r="I18" s="39"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="N18" s="32" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>6</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="A19" s="7">
+        <v>6</v>
+      </c>
+      <c r="B19" s="7">
         <v>6</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="7">
         <v>108</v>
       </c>
       <c r="E19" s="12">
+        <v>5.4315765000363898E-2</v>
+      </c>
+      <c r="F19" s="10">
+        <v>4.1771525637975904</v>
+      </c>
+      <c r="G19" s="10">
+        <v>6.0419980721123302E-5</v>
+      </c>
+      <c r="I19" s="37">
+        <v>9</v>
+      </c>
+      <c r="J19" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="K19" s="14">
+        <v>5.9719290995810005E-4</v>
+      </c>
+      <c r="L19" s="14">
+        <v>6.1873933427599999E-4</v>
+      </c>
+      <c r="M19" s="14">
+        <v>1.523367447362E-3</v>
+      </c>
+      <c r="N19" s="26">
+        <v>1.5399793559194999E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2">
+        <v>6</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="7">
+        <v>108</v>
+      </c>
+      <c r="E20" s="12">
         <v>3.5337460591478298E-2</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F20" s="10">
         <v>2.98291024159405</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G20" s="10">
         <v>3.5367985366198001E-3</v>
       </c>
-      <c r="I19" s="43"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="20" t="s">
+      <c r="I20" s="38"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="L19" s="20" t="s">
+      <c r="L20" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="M19" s="20" t="s">
+      <c r="M20" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="N19" s="31" t="s">
+      <c r="N20" s="27" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>6</v>
-      </c>
-      <c r="B20" s="6">
-        <v>9</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="6">
-        <v>105</v>
-      </c>
-      <c r="E20" s="11">
-        <v>1.99711867006667E-2</v>
-      </c>
-      <c r="F20" s="9">
-        <v>1.20457814144487</v>
-      </c>
-      <c r="G20" s="9">
-        <v>0.231100321207518</v>
-      </c>
-      <c r="I20" s="43"/>
-      <c r="J20" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="32">
-        <v>2.8474975298435901E-2</v>
-      </c>
-      <c r="L20" s="32">
-        <v>4.1623593254200397E-2</v>
-      </c>
-      <c r="M20" s="32">
-        <v>4.0294606718451698E-2</v>
-      </c>
-      <c r="N20" s="33">
-        <v>4.1963339851818701E-2</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -2349,109 +2566,111 @@
         <v>9</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D21" s="6">
         <v>105</v>
       </c>
       <c r="E21" s="11">
-        <v>6.03256929965394E-2</v>
+        <v>1.99711867006667E-2</v>
       </c>
       <c r="F21" s="9">
-        <v>3.6065100358000701</v>
+        <v>1.20457814144487</v>
       </c>
       <c r="G21" s="9">
-        <v>4.7856639655370002E-4</v>
-      </c>
-      <c r="I21" s="43"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="L21" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="M21" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="N21" s="34" t="s">
-        <v>33</v>
+        <v>0.231100321207518</v>
+      </c>
+      <c r="I21" s="38"/>
+      <c r="J21" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="28">
+        <v>2.8474975298435901E-2</v>
+      </c>
+      <c r="L21" s="28">
+        <v>4.1623593254200397E-2</v>
+      </c>
+      <c r="M21" s="28">
+        <v>4.0294606718451698E-2</v>
+      </c>
+      <c r="N21" s="29">
+        <v>4.1963339851818701E-2</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
-        <v>6</v>
-      </c>
-      <c r="B22" s="5">
+      <c r="A22" s="6">
+        <v>6</v>
+      </c>
+      <c r="B22" s="6">
         <v>9</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="6">
         <v>105</v>
       </c>
       <c r="E22" s="11">
+        <v>6.03256929965394E-2</v>
+      </c>
+      <c r="F22" s="9">
+        <v>3.6065100358000701</v>
+      </c>
+      <c r="G22" s="9">
+        <v>4.7856639655370002E-4</v>
+      </c>
+      <c r="I22" s="38"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" s="30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>6</v>
+      </c>
+      <c r="B23" s="5">
+        <v>9</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="6">
+        <v>105</v>
+      </c>
+      <c r="E23" s="11">
         <v>4.0354506295872603E-2</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F23" s="9">
         <v>2.7064255503855201</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G23" s="9">
         <v>7.9506872459265999E-3</v>
       </c>
-      <c r="I22" s="43"/>
-      <c r="J22" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="32">
+      <c r="I23" s="38"/>
+      <c r="J23" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="28">
         <v>2.7877782388477702E-2</v>
       </c>
-      <c r="L22" s="32">
+      <c r="L23" s="28">
         <v>4.1004853919924297E-2</v>
       </c>
-      <c r="M22" s="32">
+      <c r="M23" s="28">
         <v>3.8771239271089601E-2</v>
       </c>
-      <c r="N22" s="30">
+      <c r="N23" s="26">
         <v>2.6563546292623599E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>6</v>
-      </c>
-      <c r="B23" s="7">
-        <v>12</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="7">
-        <v>102</v>
-      </c>
-      <c r="E23" s="12">
-        <v>3.0649711185840801E-2</v>
-      </c>
-      <c r="F23" s="10">
-        <v>1.5309333480479801</v>
-      </c>
-      <c r="G23" s="10">
-        <v>0.12891208974354801</v>
-      </c>
-      <c r="I23" s="44"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="L23" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="M23" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="N23" s="36" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -2462,37 +2681,33 @@
         <v>12</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" s="7">
         <v>102</v>
       </c>
       <c r="E24" s="12">
-        <v>5.3065850483251402E-2</v>
+        <v>3.0649711185840801E-2</v>
       </c>
       <c r="F24" s="10">
-        <v>2.6749590287444098</v>
+        <v>1.5309333480479801</v>
       </c>
       <c r="G24" s="10">
-        <v>8.7196464352812999E-3</v>
-      </c>
-      <c r="I24" s="42">
-        <v>12</v>
-      </c>
-      <c r="J24" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-6.2206069450507998E-3</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-6.9457633388909999E-4</v>
-      </c>
-      <c r="M24" s="14">
-        <v>1.7274350360729E-2</v>
-      </c>
-      <c r="N24" s="33">
-        <v>4.7582304856785398E-2</v>
+        <v>0.12891208974354801</v>
+      </c>
+      <c r="I24" s="39"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="M24" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="32" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -2503,72 +2718,74 @@
         <v>12</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="7">
         <v>102</v>
       </c>
       <c r="E25" s="12">
+        <v>5.3065850483251402E-2</v>
+      </c>
+      <c r="F25" s="10">
+        <v>2.6749590287444098</v>
+      </c>
+      <c r="G25" s="10">
+        <v>8.7196464352812999E-3</v>
+      </c>
+      <c r="I25" s="37">
+        <v>12</v>
+      </c>
+      <c r="J25" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="K25" s="14">
+        <v>-6.2206069450507998E-3</v>
+      </c>
+      <c r="L25" s="14">
+        <v>-6.9457633388909999E-4</v>
+      </c>
+      <c r="M25" s="14">
+        <v>1.7274350360729E-2</v>
+      </c>
+      <c r="N25" s="29">
+        <v>4.7582304856785398E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>6</v>
+      </c>
+      <c r="B26" s="7">
+        <v>12</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="7">
+        <v>102</v>
+      </c>
+      <c r="E26" s="12">
         <v>2.2416139297410601E-2</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F26" s="10">
         <v>1.2647026514538</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G26" s="10">
         <v>0.208888402471089</v>
       </c>
-      <c r="I25" s="43"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="20" t="s">
+      <c r="I26" s="38"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="L25" s="20" t="s">
+      <c r="L26" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="M25" s="20" t="s">
+      <c r="M26" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="N25" s="37" t="s">
+      <c r="N26" s="33" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
-        <v>9</v>
-      </c>
-      <c r="B26" s="6">
-        <v>3</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="6">
-        <v>108</v>
-      </c>
-      <c r="E26" s="11">
-        <v>5.9719290995810005E-4</v>
-      </c>
-      <c r="F26" s="9">
-        <v>5.2714981072726597E-2</v>
-      </c>
-      <c r="G26" s="9">
-        <v>0.95805729432186704</v>
-      </c>
-      <c r="I26" s="43"/>
-      <c r="J26" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="K26" s="14">
-        <v>1.55610672921839E-2</v>
-      </c>
-      <c r="L26" s="14">
-        <v>2.14332070845108E-2</v>
-      </c>
-      <c r="M26" s="14">
-        <v>3.3700752615642197E-2</v>
-      </c>
-      <c r="N26" s="33">
-        <v>5.05347405509049E-2</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2579,109 +2796,111 @@
         <v>3</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27" s="6">
         <v>108</v>
       </c>
       <c r="E27" s="11">
-        <v>2.8474975298435901E-2</v>
+        <v>5.9719290995810005E-4</v>
       </c>
       <c r="F27" s="9">
-        <v>3.2314643208591001</v>
+        <v>5.2714981072726597E-2</v>
       </c>
       <c r="G27" s="9">
-        <v>1.6370331429953E-3</v>
-      </c>
-      <c r="I27" s="43"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="L27" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="M27" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="N27" s="37" t="s">
-        <v>41</v>
+        <v>0.95805729432186704</v>
+      </c>
+      <c r="I27" s="38"/>
+      <c r="J27" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="14">
+        <v>1.55610672921839E-2</v>
+      </c>
+      <c r="L27" s="14">
+        <v>2.14332070845108E-2</v>
+      </c>
+      <c r="M27" s="14">
+        <v>3.3700752615642197E-2</v>
+      </c>
+      <c r="N27" s="29">
+        <v>5.05347405509049E-2</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
-        <v>9</v>
-      </c>
-      <c r="B28" s="5">
+      <c r="A28" s="6">
+        <v>9</v>
+      </c>
+      <c r="B28" s="6">
         <v>3</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="6">
         <v>108</v>
       </c>
       <c r="E28" s="11">
+        <v>2.8474975298435901E-2</v>
+      </c>
+      <c r="F28" s="9">
+        <v>3.2314643208591001</v>
+      </c>
+      <c r="G28" s="9">
+        <v>1.6370331429953E-3</v>
+      </c>
+      <c r="I28" s="38"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="N28" s="33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>9</v>
+      </c>
+      <c r="B29" s="5">
+        <v>3</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="6">
+        <v>108</v>
+      </c>
+      <c r="E29" s="11">
         <v>2.7877782388477702E-2</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F29" s="9">
         <v>2.8904916757838102</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G29" s="9">
         <v>4.6583346619845003E-3</v>
       </c>
-      <c r="I28" s="43"/>
-      <c r="J28" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="K28" s="32">
+      <c r="I29" s="38"/>
+      <c r="J29" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="28">
         <v>2.1781674237234702E-2</v>
       </c>
-      <c r="L28" s="14">
+      <c r="L29" s="14">
         <v>2.21277834183999E-2</v>
       </c>
-      <c r="M28" s="14">
+      <c r="M29" s="14">
         <v>1.6426402254913201E-2</v>
       </c>
-      <c r="N28" s="30">
+      <c r="N29" s="26">
         <v>2.9524356941194999E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
-        <v>9</v>
-      </c>
-      <c r="B29" s="7">
-        <v>6</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="7">
-        <v>105</v>
-      </c>
-      <c r="E29" s="12">
-        <v>6.1873933427599999E-4</v>
-      </c>
-      <c r="F29" s="10">
-        <v>4.4346786661663397E-2</v>
-      </c>
-      <c r="G29" s="10">
-        <v>0.96471301456515401</v>
-      </c>
-      <c r="I29" s="45"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="L29" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="M29" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="N29" s="41" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2692,78 +2911,88 @@
         <v>6</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30" s="7">
         <v>105</v>
       </c>
       <c r="E30" s="12">
-        <v>4.1623593254200397E-2</v>
+        <v>6.1873933427599999E-4</v>
       </c>
       <c r="F30" s="10">
-        <v>3.1788306862105702</v>
+        <v>4.4346786661663397E-2</v>
       </c>
       <c r="G30" s="10">
-        <v>1.9481016183373E-3</v>
-      </c>
-      <c r="K30" s="17"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
+        <v>0.96471301456515401</v>
+      </c>
+      <c r="I30" s="40"/>
+      <c r="J30" s="48"/>
+      <c r="K30" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="L30" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="M30" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="N30" s="36" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>9</v>
-      </c>
-      <c r="B31" s="2">
+      <c r="A31" s="7">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
         <v>6</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="7">
         <v>105</v>
       </c>
       <c r="E31" s="12">
+        <v>4.1623593254200397E-2</v>
+      </c>
+      <c r="F31" s="10">
+        <v>3.1788306862105702</v>
+      </c>
+      <c r="G31" s="10">
+        <v>1.9481016183373E-3</v>
+      </c>
+      <c r="K31" s="17"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>9</v>
+      </c>
+      <c r="B32" s="2">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="7">
+        <v>105</v>
+      </c>
+      <c r="E32" s="12">
         <v>4.1004853919924297E-2</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F32" s="10">
         <v>3.2691054510320399</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G32" s="10">
         <v>1.4631170676755001E-3</v>
       </c>
-      <c r="K31" s="18"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>9</v>
-      </c>
-      <c r="B32" s="6">
-        <v>9</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="6">
-        <v>102</v>
-      </c>
-      <c r="E32" s="11">
-        <v>1.523367447362E-3</v>
-      </c>
-      <c r="F32" s="9">
-        <v>9.0674662684546395E-2</v>
-      </c>
-      <c r="G32" s="9">
-        <v>0.92793068806257695</v>
-      </c>
-      <c r="K32" s="17"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
@@ -2773,78 +3002,78 @@
         <v>9</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D33" s="6">
         <v>102</v>
       </c>
       <c r="E33" s="11">
-        <v>4.0294606718451698E-2</v>
+        <v>1.523367447362E-3</v>
       </c>
       <c r="F33" s="9">
-        <v>2.4803654449841401</v>
+        <v>9.0674662684546395E-2</v>
       </c>
       <c r="G33" s="9">
-        <v>1.47777782253665E-2</v>
-      </c>
-      <c r="K33" s="18"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
+        <v>0.92793068806257695</v>
+      </c>
+      <c r="K33" s="17"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
-        <v>9</v>
-      </c>
-      <c r="B34" s="5">
+      <c r="A34" s="6">
+        <v>9</v>
+      </c>
+      <c r="B34" s="6">
         <v>9</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="6">
         <v>102</v>
       </c>
       <c r="E34" s="11">
+        <v>4.0294606718451698E-2</v>
+      </c>
+      <c r="F34" s="9">
+        <v>2.4803654449841401</v>
+      </c>
+      <c r="G34" s="9">
+        <v>1.47777782253665E-2</v>
+      </c>
+      <c r="K34" s="18"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="16"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>9</v>
+      </c>
+      <c r="B35" s="5">
+        <v>9</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="6">
+        <v>102</v>
+      </c>
+      <c r="E35" s="11">
         <v>3.8771239271089601E-2</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F35" s="9">
         <v>2.4818415957859701</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G35" s="9">
         <v>1.4720291072391501E-2</v>
       </c>
-      <c r="K34" s="17"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
-        <v>9</v>
-      </c>
-      <c r="B35" s="7">
-        <v>12</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="7">
-        <v>99</v>
-      </c>
-      <c r="E35" s="12">
-        <v>1.5399793559194999E-2</v>
-      </c>
-      <c r="F35" s="10">
-        <v>0.78676070623234695</v>
-      </c>
-      <c r="G35" s="10">
-        <v>0.43332043259999797</v>
-      </c>
-      <c r="K35" s="18"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="16"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
@@ -2854,24 +3083,24 @@
         <v>12</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D36" s="7">
         <v>99</v>
       </c>
       <c r="E36" s="12">
-        <v>4.1963339851818701E-2</v>
+        <v>1.5399793559194999E-2</v>
       </c>
       <c r="F36" s="10">
-        <v>1.9830952728584299</v>
+        <v>0.78676070623234695</v>
       </c>
       <c r="G36" s="10">
-        <v>5.0155542116857701E-2</v>
-      </c>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
+        <v>0.43332043259999797</v>
+      </c>
+      <c r="K36" s="18"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
@@ -2881,51 +3110,51 @@
         <v>12</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="7">
         <v>99</v>
       </c>
       <c r="E37" s="12">
+        <v>4.1963339851818701E-2</v>
+      </c>
+      <c r="F37" s="10">
+        <v>1.9830952728584299</v>
+      </c>
+      <c r="G37" s="10">
+        <v>5.0155542116857701E-2</v>
+      </c>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7">
+        <v>12</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="7">
+        <v>99</v>
+      </c>
+      <c r="E38" s="12">
         <v>2.6563546292623599E-2</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F38" s="10">
         <v>1.36957393403213</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G38" s="10">
         <v>0.17395011282650499</v>
       </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
-        <v>12</v>
-      </c>
-      <c r="B38" s="6">
-        <v>3</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="6">
-        <v>105</v>
-      </c>
-      <c r="E38" s="11">
-        <v>-6.2206069450507998E-3</v>
-      </c>
-      <c r="F38" s="9">
-        <v>-0.53583211527644603</v>
-      </c>
-      <c r="G38" s="9">
-        <v>0.59321870892864503</v>
-      </c>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+      <c r="N38" s="16"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
@@ -2935,78 +3164,78 @@
         <v>3</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D39" s="6">
         <v>105</v>
       </c>
       <c r="E39" s="11">
-        <v>1.55610672921839E-2</v>
+        <v>-6.2206069450507998E-3</v>
       </c>
       <c r="F39" s="9">
-        <v>1.7682394061761799</v>
+        <v>-0.53583211527644603</v>
       </c>
       <c r="G39" s="9">
-        <v>7.9953173706632505E-2</v>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
+        <v>0.59321870892864503</v>
+      </c>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="14"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="5">
-        <v>12</v>
-      </c>
-      <c r="B40" s="5">
+      <c r="A40" s="6">
+        <v>12</v>
+      </c>
+      <c r="B40" s="6">
         <v>3</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="6">
         <v>105</v>
       </c>
       <c r="E40" s="11">
+        <v>1.55610672921839E-2</v>
+      </c>
+      <c r="F40" s="9">
+        <v>1.7682394061761799</v>
+      </c>
+      <c r="G40" s="9">
+        <v>7.9953173706632505E-2</v>
+      </c>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
+      <c r="N40" s="16"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>12</v>
+      </c>
+      <c r="B41" s="5">
+        <v>3</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="6">
+        <v>105</v>
+      </c>
+      <c r="E41" s="11">
         <v>2.1781674237234702E-2</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F41" s="9">
         <v>2.18444160507469</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G41" s="9">
         <v>3.1175742226854802E-2</v>
       </c>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
-        <v>12</v>
-      </c>
-      <c r="B41" s="7">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="7">
-        <v>102</v>
-      </c>
-      <c r="E41" s="12">
-        <v>-6.9457633388909999E-4</v>
-      </c>
-      <c r="F41" s="10">
-        <v>-4.6921789058382297E-2</v>
-      </c>
-      <c r="G41" s="10">
-        <v>0.96266821624608201</v>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="16"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="14"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
@@ -3016,24 +3245,24 @@
         <v>6</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D42" s="7">
         <v>102</v>
       </c>
       <c r="E42" s="12">
-        <v>2.14332070845108E-2</v>
+        <v>-6.9457633388909999E-4</v>
       </c>
       <c r="F42" s="10">
-        <v>1.5868298092322599</v>
+        <v>-4.6921789058382297E-2</v>
       </c>
       <c r="G42" s="10">
-        <v>0.11567711128970599</v>
-      </c>
-      <c r="K42" s="17"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="14"/>
+        <v>0.96266821624608201</v>
+      </c>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="16"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
@@ -3043,51 +3272,51 @@
         <v>6</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43" s="7">
         <v>102</v>
       </c>
       <c r="E43" s="12">
+        <v>2.14332070845108E-2</v>
+      </c>
+      <c r="F43" s="10">
+        <v>1.5868298092322599</v>
+      </c>
+      <c r="G43" s="10">
+        <v>0.11567711128970599</v>
+      </c>
+      <c r="K43" s="17"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="14"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>12</v>
+      </c>
+      <c r="B44" s="7">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="7">
+        <v>102</v>
+      </c>
+      <c r="E44" s="12">
         <v>2.21277834183999E-2</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F44" s="10">
         <v>1.5686371069098901</v>
       </c>
-      <c r="G43" s="10">
+      <c r="G44" s="10">
         <v>0.119860281551464</v>
       </c>
-      <c r="K43" s="18"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="16"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
-        <v>12</v>
-      </c>
-      <c r="B44" s="6">
-        <v>9</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" s="6">
-        <v>99</v>
-      </c>
-      <c r="E44" s="11">
-        <v>1.7274350360729E-2</v>
-      </c>
-      <c r="F44" s="9">
-        <v>0.96718798430602604</v>
-      </c>
-      <c r="G44" s="9">
-        <v>0.335830909036957</v>
-      </c>
-      <c r="K44" s="17"/>
-      <c r="L44" s="14"/>
-      <c r="M44" s="14"/>
-      <c r="N44" s="14"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="16"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -3097,24 +3326,24 @@
         <v>9</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D45" s="6">
         <v>99</v>
       </c>
       <c r="E45" s="11">
-        <v>3.3700752615642197E-2</v>
+        <v>1.7274350360729E-2</v>
       </c>
       <c r="F45" s="9">
-        <v>1.9111876517641899</v>
+        <v>0.96718798430602604</v>
       </c>
       <c r="G45" s="9">
-        <v>5.8902534117065301E-2</v>
-      </c>
-      <c r="K45" s="18"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="16"/>
+        <v>0.335830909036957</v>
+      </c>
+      <c r="K45" s="17"/>
+      <c r="L45" s="14"/>
+      <c r="M45" s="14"/>
+      <c r="N45" s="14"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -3124,51 +3353,51 @@
         <v>9</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D46" s="6">
         <v>99</v>
       </c>
       <c r="E46" s="11">
+        <v>3.3700752615642197E-2</v>
+      </c>
+      <c r="F46" s="9">
+        <v>1.9111876517641899</v>
+      </c>
+      <c r="G46" s="9">
+        <v>5.8902534117065301E-2</v>
+      </c>
+      <c r="K46" s="18"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>12</v>
+      </c>
+      <c r="B47" s="6">
+        <v>9</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="6">
+        <v>99</v>
+      </c>
+      <c r="E47" s="11">
         <v>1.6426402254913201E-2</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F47" s="9">
         <v>0.93121947420209605</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G47" s="9">
         <v>0.35402843630614</v>
       </c>
-      <c r="K46" s="17"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="14"/>
-      <c r="N46" s="14"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="7">
-        <v>12</v>
-      </c>
-      <c r="B47" s="7">
-        <v>12</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="7">
-        <v>96</v>
-      </c>
-      <c r="E47" s="12">
-        <v>4.7582304856785398E-2</v>
-      </c>
-      <c r="F47" s="10">
-        <v>2.1319726491645499</v>
-      </c>
-      <c r="G47" s="10">
-        <v>3.5588701036567499E-2</v>
-      </c>
-      <c r="K47" s="18"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
+      <c r="N47" s="14"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
@@ -3178,24 +3407,24 @@
         <v>12</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D48" s="7">
         <v>96</v>
       </c>
       <c r="E48" s="12">
-        <v>5.05347405509049E-2</v>
+        <v>4.7582304856785398E-2</v>
       </c>
       <c r="F48" s="10">
-        <v>2.24675213526971</v>
+        <v>2.1319726491645499</v>
       </c>
       <c r="G48" s="10">
-        <v>2.6971310954366098E-2</v>
-      </c>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
-      <c r="N48" s="14"/>
+        <v>3.5588701036567499E-2</v>
+      </c>
+      <c r="K48" s="18"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
@@ -3205,112 +3434,149 @@
         <v>12</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D49" s="7">
         <v>96</v>
       </c>
       <c r="E49" s="12">
+        <v>5.05347405509049E-2</v>
+      </c>
+      <c r="F49" s="10">
+        <v>2.24675213526971</v>
+      </c>
+      <c r="G49" s="10">
+        <v>2.6971310954366098E-2</v>
+      </c>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>12</v>
+      </c>
+      <c r="B50" s="7">
+        <v>12</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="7">
+        <v>96</v>
+      </c>
+      <c r="E50" s="12">
         <v>2.9524356941194999E-3</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F50" s="10">
         <v>0.12530451887434399</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G50" s="10">
         <v>0.90054726036784105</v>
       </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="16"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
-      <c r="N50" s="14"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="16"/>
+      <c r="N50" s="16"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="16"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="14"/>
+      <c r="M51" s="14"/>
+      <c r="N51" s="14"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-      <c r="M52" s="14"/>
-      <c r="N52" s="14"/>
+      <c r="K52" s="16"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="16"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="16"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="14"/>
+      <c r="M53" s="14"/>
+      <c r="N53" s="14"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
-      <c r="N54" s="14"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+      <c r="N54" s="16"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="16"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="14"/>
+      <c r="N55" s="14"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="14"/>
-      <c r="N56" s="14"/>
+      <c r="K56" s="16"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="16"/>
+      <c r="N56" s="16"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="16"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="14"/>
+      <c r="M57" s="14"/>
+      <c r="N57" s="14"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="14"/>
-      <c r="N58" s="14"/>
+      <c r="K58" s="16"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
+      <c r="N58" s="16"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="16"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+      <c r="M59" s="14"/>
+      <c r="N59" s="14"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K60" s="16"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
+      <c r="N60" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G49" xr:uid="{828DFD01-9D50-4EA6-A7DD-A0B766D34BA5}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G49">
-      <sortCondition ref="A1"/>
+  <autoFilter ref="A2:G50" xr:uid="{828DFD01-9D50-4EA6-A7DD-A0B766D34BA5}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G50">
+      <sortCondition ref="A2"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="8">
-    <mergeCell ref="I18:I23"/>
-    <mergeCell ref="I24:I29"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="I6:I11"/>
-    <mergeCell ref="I12:I17"/>
+  <mergeCells count="18">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="I19:I24"/>
+    <mergeCell ref="I25:I30"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="I7:I12"/>
+    <mergeCell ref="I13:I18"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="E2:E1048576">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="G2:G1048576">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3321,20 +3587,2019 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60641E96-17E1-4C28-95A7-3B3EADA10A6C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="2" width="10.625" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="5" max="5" width="10.625" customWidth="1"/>
+    <col min="6" max="7" width="14" customWidth="1"/>
+    <col min="9" max="9" width="7.125" customWidth="1"/>
+    <col min="10" max="10" width="15.25" customWidth="1"/>
+    <col min="11" max="14" width="11.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6">
+        <v>3</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6">
+        <v>3</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="I4" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="43"/>
+    </row>
+    <row r="5" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="I5" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="15">
+        <v>3</v>
+      </c>
+      <c r="L5" s="15">
+        <v>6</v>
+      </c>
+      <c r="M5" s="15">
+        <v>9</v>
+      </c>
+      <c r="N5" s="25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="I6" s="49">
+        <v>3</v>
+      </c>
+      <c r="J6" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="26"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7">
+        <v>6</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="67"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="56"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="58"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="68"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="68"/>
+      <c r="N10" s="56"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="69"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="69"/>
+      <c r="N11" s="70"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>3</v>
+      </c>
+      <c r="B12" s="7">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="I12" s="37">
+        <v>6</v>
+      </c>
+      <c r="J12" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="K12" s="68"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="56"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7">
+        <v>12</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="66"/>
+      <c r="L13" s="66"/>
+      <c r="M13" s="66"/>
+      <c r="N13" s="67"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2">
+        <v>12</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="56"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>6</v>
+      </c>
+      <c r="B15" s="6">
+        <v>3</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="57"/>
+      <c r="N15" s="58"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>6</v>
+      </c>
+      <c r="B16" s="6">
+        <v>3</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="68"/>
+      <c r="L16" s="68"/>
+      <c r="M16" s="68"/>
+      <c r="N16" s="56"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>6</v>
+      </c>
+      <c r="B17" s="5">
+        <v>3</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="69"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="72"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>6</v>
+      </c>
+      <c r="B18" s="7">
+        <v>6</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="I18" s="37">
+        <v>9</v>
+      </c>
+      <c r="J18" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="K18" s="68"/>
+      <c r="L18" s="68"/>
+      <c r="M18" s="68"/>
+      <c r="N18" s="56"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>6</v>
+      </c>
+      <c r="B19" s="7">
+        <v>6</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="66"/>
+      <c r="L19" s="66"/>
+      <c r="M19" s="66"/>
+      <c r="N19" s="67"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2">
+        <v>6</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="68"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="68"/>
+      <c r="N20" s="56"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>6</v>
+      </c>
+      <c r="B21" s="6">
+        <v>9</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="58"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>6</v>
+      </c>
+      <c r="B22" s="6">
+        <v>9</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="68"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="56"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>6</v>
+      </c>
+      <c r="B23" s="5">
+        <v>9</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="69"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="72"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>6</v>
+      </c>
+      <c r="B24" s="7">
+        <v>12</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="I24" s="37">
+        <v>12</v>
+      </c>
+      <c r="J24" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="K24" s="68"/>
+      <c r="L24" s="68"/>
+      <c r="M24" s="68"/>
+      <c r="N24" s="56"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>6</v>
+      </c>
+      <c r="B25" s="7">
+        <v>12</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="66"/>
+      <c r="L25" s="66"/>
+      <c r="M25" s="66"/>
+      <c r="N25" s="73"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>6</v>
+      </c>
+      <c r="B26" s="7">
+        <v>12</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="68"/>
+      <c r="L26" s="68"/>
+      <c r="M26" s="68"/>
+      <c r="N26" s="56"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>9</v>
+      </c>
+      <c r="B27" s="6">
+        <v>3</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="66"/>
+      <c r="L27" s="66"/>
+      <c r="M27" s="66"/>
+      <c r="N27" s="73"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>9</v>
+      </c>
+      <c r="B28" s="6">
+        <v>3</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="68"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="68"/>
+      <c r="N28" s="56"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>9</v>
+      </c>
+      <c r="B29" s="5">
+        <v>3</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="36"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>6</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>6</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>9</v>
+      </c>
+      <c r="B32" s="2">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>9</v>
+      </c>
+      <c r="B33" s="6">
+        <v>9</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>9</v>
+      </c>
+      <c r="B34" s="6">
+        <v>9</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>9</v>
+      </c>
+      <c r="B35" s="5">
+        <v>9</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="6"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7">
+        <v>12</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="7"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>9</v>
+      </c>
+      <c r="B37" s="7">
+        <v>12</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="7"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7">
+        <v>12</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="7"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>12</v>
+      </c>
+      <c r="B39" s="6">
+        <v>3</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="6"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>12</v>
+      </c>
+      <c r="B40" s="6">
+        <v>3</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="6"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>12</v>
+      </c>
+      <c r="B41" s="5">
+        <v>3</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="6"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>12</v>
+      </c>
+      <c r="B42" s="7">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="7"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>12</v>
+      </c>
+      <c r="B43" s="7">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="7"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>12</v>
+      </c>
+      <c r="B44" s="7">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="7"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>12</v>
+      </c>
+      <c r="B45" s="6">
+        <v>9</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="6"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>12</v>
+      </c>
+      <c r="B46" s="6">
+        <v>9</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="6"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>12</v>
+      </c>
+      <c r="B47" s="6">
+        <v>9</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="6"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>12</v>
+      </c>
+      <c r="B48" s="7">
+        <v>12</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="7"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>12</v>
+      </c>
+      <c r="B49" s="7">
+        <v>12</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="7"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>12</v>
+      </c>
+      <c r="B50" s="7">
+        <v>12</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="7"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="I24:I29"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="I12:I17"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="I18:I23"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="I6:I11"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="J10:J11"/>
+  </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
+  <conditionalFormatting sqref="E2">
+    <cfRule type="cellIs" dxfId="20" priority="11" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="12" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2">
+    <cfRule type="cellIs" dxfId="18" priority="10" operator="lessThan">
+      <formula>0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E50">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G50">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA12766-CA57-4195-AB5D-D953190D2612}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="13.375" customWidth="1"/>
+    <col min="6" max="6" width="9.75" customWidth="1"/>
+    <col min="7" max="7" width="10.75" customWidth="1"/>
+    <col min="8" max="8" width="2.75" customWidth="1"/>
+    <col min="9" max="9" width="7.25" customWidth="1"/>
+    <col min="10" max="10" width="14.875" customWidth="1"/>
+    <col min="11" max="14" width="12.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+    </row>
+    <row r="3" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6">
+        <v>3</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6">
+        <v>114</v>
+      </c>
+      <c r="E3" s="11">
+        <v>1.2676155267131099E-3</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0.127652013401201</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0.89865125913546695</v>
+      </c>
+      <c r="I3" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="59">
+        <v>3</v>
+      </c>
+      <c r="L3" s="59">
+        <v>6</v>
+      </c>
+      <c r="M3" s="59">
+        <v>9</v>
+      </c>
+      <c r="N3" s="60">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6">
+        <v>3</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6">
+        <v>114</v>
+      </c>
+      <c r="E4" s="11">
+        <v>2.4591457834495602E-2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>2.9832338535301401</v>
+      </c>
+      <c r="G4" s="9">
+        <v>3.4952799955571198E-3</v>
+      </c>
+      <c r="I4" s="61">
+        <v>3</v>
+      </c>
+      <c r="J4" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="54">
+        <f>E3</f>
+        <v>1.2676155267131099E-3</v>
+      </c>
+      <c r="L4" s="54">
+        <f>E6</f>
+        <v>-2.2454643896498601E-3</v>
+      </c>
+      <c r="M4" s="54">
+        <f>E9</f>
+        <v>-4.9802207879865498E-3</v>
+      </c>
+      <c r="N4" s="26">
+        <f>E12</f>
+        <v>3.1250864080159101E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="6">
+        <v>114</v>
+      </c>
+      <c r="E5" s="11">
+        <v>2.3323842307782498E-2</v>
+      </c>
+      <c r="F5" s="9">
+        <v>3.6673643552384498</v>
+      </c>
+      <c r="G5" s="9">
+        <v>3.7518090649497199E-4</v>
+      </c>
+      <c r="I5" s="62"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="20">
+        <f>F3</f>
+        <v>0.127652013401201</v>
+      </c>
+      <c r="L5" s="20">
+        <f>F6</f>
+        <v>-0.19245858023207699</v>
+      </c>
+      <c r="M5" s="20">
+        <f>F9</f>
+        <v>-0.38114629758028701</v>
+      </c>
+      <c r="N5" s="27">
+        <f>F12</f>
+        <v>1.9490597473919499E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7">
+        <v>111</v>
+      </c>
+      <c r="E6" s="12">
+        <v>-2.2454643896498601E-3</v>
+      </c>
+      <c r="F6" s="10">
+        <v>-0.19245858023207699</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0.84773787571883197</v>
+      </c>
+      <c r="I6" s="62"/>
+      <c r="J6" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" s="55">
+        <f>E4</f>
+        <v>2.4591457834495602E-2</v>
+      </c>
+      <c r="L6" s="55">
+        <f>E7</f>
+        <v>4.6514485130783302E-2</v>
+      </c>
+      <c r="M6" s="55">
+        <f>E10</f>
+        <v>6.2453828535481599E-2</v>
+      </c>
+      <c r="N6" s="29">
+        <f>E12</f>
+        <v>3.1250864080159101E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7">
+        <v>6</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7">
+        <v>111</v>
+      </c>
+      <c r="E7" s="12">
+        <v>4.6514485130783302E-2</v>
+      </c>
+      <c r="F7" s="10">
+        <v>3.8905337675188099</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1.7170331339624899E-4</v>
+      </c>
+      <c r="I7" s="62"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="57">
+        <f>F4</f>
+        <v>2.9832338535301401</v>
+      </c>
+      <c r="L7" s="57">
+        <f>F7</f>
+        <v>3.8905337675188099</v>
+      </c>
+      <c r="M7" s="57">
+        <f>F10</f>
+        <v>4.20880434785182</v>
+      </c>
+      <c r="N7" s="58">
+        <f>F13</f>
+        <v>3.7415387914354601</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="7">
+        <v>111</v>
+      </c>
+      <c r="E8" s="12">
+        <v>4.8759949520433103E-2</v>
+      </c>
+      <c r="F8" s="10">
+        <v>7.1727799005828103</v>
+      </c>
+      <c r="G8" s="10">
+        <v>9.0227491087471003E-11</v>
+      </c>
+      <c r="I8" s="62"/>
+      <c r="J8" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="55">
+        <f>E5</f>
+        <v>2.3323842307782498E-2</v>
+      </c>
+      <c r="L8" s="55">
+        <f>E8</f>
+        <v>4.8759949520433103E-2</v>
+      </c>
+      <c r="M8" s="55">
+        <f>E11</f>
+        <v>6.7434049323468095E-2</v>
+      </c>
+      <c r="N8" s="29">
+        <f>E12</f>
+        <v>3.1250864080159101E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="6">
+        <v>108</v>
+      </c>
+      <c r="E9" s="11">
+        <v>-4.9802207879865498E-3</v>
+      </c>
+      <c r="F9" s="9">
+        <v>-0.38114629758028701</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0.70385043948405301</v>
+      </c>
+      <c r="I9" s="63"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="23">
+        <f>F5</f>
+        <v>3.6673643552384498</v>
+      </c>
+      <c r="L9" s="23">
+        <f>F8</f>
+        <v>7.1727799005828103</v>
+      </c>
+      <c r="M9" s="23">
+        <f>F11</f>
+        <v>8.6905835945024705</v>
+      </c>
+      <c r="N9" s="31">
+        <f>F14</f>
+        <v>7.0267777188403997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="6">
+        <v>108</v>
+      </c>
+      <c r="E10" s="11">
+        <v>6.2453828535481599E-2</v>
+      </c>
+      <c r="F10" s="9">
+        <v>4.20880434785182</v>
+      </c>
+      <c r="G10" s="9">
+        <v>5.3598713981954997E-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="6">
+        <v>108</v>
+      </c>
+      <c r="E11" s="11">
+        <v>6.7434049323468095E-2</v>
+      </c>
+      <c r="F11" s="9">
+        <v>8.6905835945024705</v>
+      </c>
+      <c r="G11" s="9">
+        <v>4.6078621241686099E-14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>3</v>
+      </c>
+      <c r="B12" s="7">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="7">
+        <v>105</v>
+      </c>
+      <c r="E12" s="12">
+        <v>3.1250864080159101E-4</v>
+      </c>
+      <c r="F12" s="10">
+        <v>1.9490597473919499E-2</v>
+      </c>
+      <c r="G12" s="10">
+        <v>0.98448708216231096</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7">
+        <v>12</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="7">
+        <v>105</v>
+      </c>
+      <c r="E13" s="12">
+        <v>6.6481726661294302E-2</v>
+      </c>
+      <c r="F13" s="10">
+        <v>3.7415387914354601</v>
+      </c>
+      <c r="G13" s="10">
+        <v>2.9983269664811098E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2">
+        <v>12</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="7">
+        <v>105</v>
+      </c>
+      <c r="E14" s="12">
+        <v>6.6169218020492707E-2</v>
+      </c>
+      <c r="F14" s="10">
+        <v>7.0267777188403997</v>
+      </c>
+      <c r="G14" s="10">
+        <v>2.2733299034642299E-10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="50"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="50"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="64"/>
+    </row>
+    <row r="19" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <v>3</v>
+      </c>
+      <c r="B19" s="6">
+        <v>3</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="6">
+        <v>174</v>
+      </c>
+      <c r="E19" s="11">
+        <v>8.9648117847710498E-3</v>
+      </c>
+      <c r="F19" s="9">
+        <v>1.1263240230215701</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0.26158835276995202</v>
+      </c>
+      <c r="I19" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" s="59">
+        <v>3</v>
+      </c>
+      <c r="L19" s="59">
+        <v>6</v>
+      </c>
+      <c r="M19" s="59">
+        <v>9</v>
+      </c>
+      <c r="N19" s="60">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>3</v>
+      </c>
+      <c r="B20" s="6">
+        <v>3</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="6">
+        <v>174</v>
+      </c>
+      <c r="E20" s="11">
+        <v>3.6456284904080198E-2</v>
+      </c>
+      <c r="F20" s="9">
+        <v>4.9316087626070901</v>
+      </c>
+      <c r="G20" s="9">
+        <v>1.9022683024534E-6</v>
+      </c>
+      <c r="I20" s="61">
+        <v>3</v>
+      </c>
+      <c r="J20" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="K20" s="54">
+        <f>E19</f>
+        <v>8.9648117847710498E-3</v>
+      </c>
+      <c r="L20" s="54">
+        <f>E22</f>
+        <v>1.9186431825705601E-2</v>
+      </c>
+      <c r="M20" s="54">
+        <f>E25</f>
+        <v>3.1641119197947001E-2</v>
+      </c>
+      <c r="N20" s="26">
+        <f>E28</f>
+        <v>5.52136466982436E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>3</v>
+      </c>
+      <c r="B21" s="5">
+        <v>3</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="6">
+        <v>174</v>
+      </c>
+      <c r="E21" s="11">
+        <v>2.74914731193092E-2</v>
+      </c>
+      <c r="F21" s="9">
+        <v>5.48900911918963</v>
+      </c>
+      <c r="G21" s="9">
+        <v>1.41941805723813E-7</v>
+      </c>
+      <c r="I21" s="62"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="20">
+        <f>F19</f>
+        <v>1.1263240230215701</v>
+      </c>
+      <c r="L21" s="20">
+        <f>F22</f>
+        <v>1.9343605558016199</v>
+      </c>
+      <c r="M21" s="20">
+        <f>F25</f>
+        <v>2.60146713298073</v>
+      </c>
+      <c r="N21" s="27">
+        <f>F28</f>
+        <v>3.6216418290305401</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>3</v>
+      </c>
+      <c r="B22" s="7">
+        <v>6</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="7">
+        <v>171</v>
+      </c>
+      <c r="E22" s="12">
+        <v>1.9186431825705601E-2</v>
+      </c>
+      <c r="F22" s="10">
+        <v>1.9343605558016199</v>
+      </c>
+      <c r="G22" s="10">
+        <v>5.4729223964147297E-2</v>
+      </c>
+      <c r="I22" s="62"/>
+      <c r="J22" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="55">
+        <f>E20</f>
+        <v>3.6456284904080198E-2</v>
+      </c>
+      <c r="L22" s="55">
+        <f>E23</f>
+        <v>7.1496430351053006E-2</v>
+      </c>
+      <c r="M22" s="55">
+        <f>E26</f>
+        <v>9.9917898969015498E-2</v>
+      </c>
+      <c r="N22" s="29">
+        <f>E29</f>
+        <v>0.119470995092858</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>3</v>
+      </c>
+      <c r="B23" s="7">
+        <v>6</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="7">
+        <v>171</v>
+      </c>
+      <c r="E23" s="12">
+        <v>7.1496430351053006E-2</v>
+      </c>
+      <c r="F23" s="10">
+        <v>6.7041206290680799</v>
+      </c>
+      <c r="G23" s="10">
+        <v>2.8649193162989599E-10</v>
+      </c>
+      <c r="I23" s="62"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="57">
+        <f>F20</f>
+        <v>4.9316087626070901</v>
+      </c>
+      <c r="L23" s="57">
+        <f>F23</f>
+        <v>6.7041206290680799</v>
+      </c>
+      <c r="M23" s="57">
+        <f>F26</f>
+        <v>7.7215872485542496</v>
+      </c>
+      <c r="N23" s="58">
+        <f>F29</f>
+        <v>7.50325410032573</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>3</v>
+      </c>
+      <c r="B24" s="2">
+        <v>6</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="7">
+        <v>171</v>
+      </c>
+      <c r="E24" s="12">
+        <v>5.2309998525347297E-2</v>
+      </c>
+      <c r="F24" s="10">
+        <v>8.5639548720690595</v>
+      </c>
+      <c r="G24" s="10">
+        <v>6.3190312413867199E-15</v>
+      </c>
+      <c r="I24" s="62"/>
+      <c r="J24" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="55">
+        <f>E21</f>
+        <v>2.74914731193092E-2</v>
+      </c>
+      <c r="L24" s="55">
+        <f>E24</f>
+        <v>5.2309998525347297E-2</v>
+      </c>
+      <c r="M24" s="55">
+        <f>E27</f>
+        <v>6.8276779771068496E-2</v>
+      </c>
+      <c r="N24" s="29">
+        <f>E30</f>
+        <v>6.4257348394614999E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>3</v>
+      </c>
+      <c r="B25" s="6">
+        <v>9</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="6">
+        <v>168</v>
+      </c>
+      <c r="E25" s="11">
+        <v>3.1641119197947001E-2</v>
+      </c>
+      <c r="F25" s="9">
+        <v>2.60146713298073</v>
+      </c>
+      <c r="G25" s="9">
+        <v>1.01161296606066E-2</v>
+      </c>
+      <c r="I25" s="63"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="23">
+        <f>F21</f>
+        <v>5.48900911918963</v>
+      </c>
+      <c r="L25" s="23">
+        <f>F24</f>
+        <v>8.5639548720690595</v>
+      </c>
+      <c r="M25" s="23">
+        <f>F27</f>
+        <v>8.8781796101653701</v>
+      </c>
+      <c r="N25" s="31">
+        <f>F30</f>
+        <v>7.1660071590778198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>3</v>
+      </c>
+      <c r="B26" s="6">
+        <v>9</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="6">
+        <v>168</v>
+      </c>
+      <c r="E26" s="11">
+        <v>9.9917898969015498E-2</v>
+      </c>
+      <c r="F26" s="9">
+        <v>7.7215872485542496</v>
+      </c>
+      <c r="G26" s="9">
+        <v>1.00440591326992E-12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>3</v>
+      </c>
+      <c r="B27" s="5">
+        <v>9</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="6">
+        <v>168</v>
+      </c>
+      <c r="E27" s="11">
+        <v>6.8276779771068496E-2</v>
+      </c>
+      <c r="F27" s="9">
+        <v>8.8781796101653701</v>
+      </c>
+      <c r="G27" s="9">
+        <v>1.0271044282789199E-15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>3</v>
+      </c>
+      <c r="B28" s="7">
+        <v>12</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="7">
+        <v>165</v>
+      </c>
+      <c r="E28" s="12">
+        <v>5.52136466982436E-2</v>
+      </c>
+      <c r="F28" s="10">
+        <v>3.6216418290305401</v>
+      </c>
+      <c r="G28" s="10">
+        <v>3.8989453950004702E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>3</v>
+      </c>
+      <c r="B29" s="7">
+        <v>12</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="7">
+        <v>165</v>
+      </c>
+      <c r="E29" s="12">
+        <v>0.119470995092858</v>
+      </c>
+      <c r="F29" s="10">
+        <v>7.50325410032573</v>
+      </c>
+      <c r="G29" s="10">
+        <v>3.7410479353997401E-12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>3</v>
+      </c>
+      <c r="B30" s="2">
+        <v>12</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="7">
+        <v>165</v>
+      </c>
+      <c r="E30" s="12">
+        <v>6.4257348394614999E-2</v>
+      </c>
+      <c r="F30" s="10">
+        <v>7.1660071590778198</v>
+      </c>
+      <c r="G30" s="10">
+        <v>2.49001927703697E-11</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="I20:I25"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="I18:N18"/>
+    <mergeCell ref="I2:N2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="I4:I9"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J8:J9"/>
+  </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
+  <conditionalFormatting sqref="E2">
+    <cfRule type="cellIs" dxfId="14" priority="11" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="12" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2">
+    <cfRule type="cellIs" dxfId="12" priority="10" operator="lessThan">
+      <formula>0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E18">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="lessThan">
+      <formula>0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E14">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G14">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThan">
+      <formula>0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19:E30">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19:G30">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+      <formula>0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/analysis/momentumNew/mergeTtestResult/merged_t_test.xlsx
+++ b/data/analysis/momentumNew/mergeTtestResult/merged_t_test.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Han\學習\金融策略\分析程式\data\analysis\momentumNew\mergeTtestResult\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C463C36D-CFEB-4182-8491-035EBF9B57C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97A34F6-063A-4C18-8550-F09C7462017C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{79B926A8-815C-4ADE-A3A1-103001E1D343}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{79B926A8-815C-4ADE-A3A1-103001E1D343}"/>
   </bookViews>
   <sheets>
     <sheet name="mv150_10years" sheetId="1" r:id="rId1"/>
     <sheet name="mv150_15years" sheetId="2" r:id="rId2"/>
     <sheet name="priceOver10" sheetId="3" r:id="rId3"/>
+    <sheet name="工作表1" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mv150_10years!$A$2:$G$50</definedName>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="144">
   <si>
     <t>remark</t>
   </si>
@@ -179,6 +180,290 @@
   </si>
   <si>
     <t>2010~2024</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>0.13%</t>
+  </si>
+  <si>
+    <t>-0.22%</t>
+  </si>
+  <si>
+    <t>-0.50%</t>
+  </si>
+  <si>
+    <t>0.03%</t>
+  </si>
+  <si>
+    <t>(-0.19)</t>
+  </si>
+  <si>
+    <t>(-0.38)</t>
+  </si>
+  <si>
+    <t>(0.02)</t>
+  </si>
+  <si>
+    <t>2.46%</t>
+  </si>
+  <si>
+    <t>4.65%</t>
+  </si>
+  <si>
+    <t>6.25%</t>
+  </si>
+  <si>
+    <t>6.65%</t>
+  </si>
+  <si>
+    <t>(3.89)</t>
+  </si>
+  <si>
+    <t>(4.21)</t>
+  </si>
+  <si>
+    <t>(3.74)</t>
+  </si>
+  <si>
+    <t>2.33%</t>
+  </si>
+  <si>
+    <t>4.88%</t>
+  </si>
+  <si>
+    <t>6.74%</t>
+  </si>
+  <si>
+    <t>6.62%</t>
+  </si>
+  <si>
+    <t>(3.67)</t>
+  </si>
+  <si>
+    <t>(7.17)</t>
+  </si>
+  <si>
+    <t>(8.69)</t>
+  </si>
+  <si>
+    <t>(7.03)</t>
+  </si>
+  <si>
+    <t>-0.14%</t>
+  </si>
+  <si>
+    <t>-0.64%</t>
+  </si>
+  <si>
+    <t>-0.53%</t>
+  </si>
+  <si>
+    <t>0.33%</t>
+  </si>
+  <si>
+    <t>(-0.13)</t>
+  </si>
+  <si>
+    <t>(-0.53)</t>
+  </si>
+  <si>
+    <t>(-0.37)</t>
+  </si>
+  <si>
+    <t>(0.20)</t>
+  </si>
+  <si>
+    <t>2.84%</t>
+  </si>
+  <si>
+    <t>5.34%</t>
+  </si>
+  <si>
+    <t>6.54%</t>
+  </si>
+  <si>
+    <t>6.61%</t>
+  </si>
+  <si>
+    <t>(3.31)</t>
+  </si>
+  <si>
+    <t>(4.36)</t>
+  </si>
+  <si>
+    <t>(4.27)</t>
+  </si>
+  <si>
+    <t>(3.53)</t>
+  </si>
+  <si>
+    <t>2.99%</t>
+  </si>
+  <si>
+    <t>5.99%</t>
+  </si>
+  <si>
+    <t>7.06%</t>
+  </si>
+  <si>
+    <t>6.28%</t>
+  </si>
+  <si>
+    <t>(4.46)</t>
+  </si>
+  <si>
+    <t>(8.13)</t>
+  </si>
+  <si>
+    <t>(8.09)</t>
+  </si>
+  <si>
+    <t>(5.58)</t>
+  </si>
+  <si>
+    <t>-0.29%</t>
+  </si>
+  <si>
+    <t>-0.41%</t>
+  </si>
+  <si>
+    <t>0.07%</t>
+  </si>
+  <si>
+    <t>2.19%</t>
+  </si>
+  <si>
+    <t>(-0.27)</t>
+  </si>
+  <si>
+    <t>(-0.31)</t>
+  </si>
+  <si>
+    <t>2.87%</t>
+  </si>
+  <si>
+    <t>4.62%</t>
+  </si>
+  <si>
+    <t>5.35%</t>
+  </si>
+  <si>
+    <t>5.29%</t>
+  </si>
+  <si>
+    <t>(3.26)</t>
+  </si>
+  <si>
+    <t>(3.83)</t>
+  </si>
+  <si>
+    <t>(3.52)</t>
+  </si>
+  <si>
+    <t>(2.81)</t>
+  </si>
+  <si>
+    <t>3.17%</t>
+  </si>
+  <si>
+    <t>5.03%</t>
+  </si>
+  <si>
+    <t>5.28%</t>
+  </si>
+  <si>
+    <t>3.10%</t>
+  </si>
+  <si>
+    <t>(4.50)</t>
+  </si>
+  <si>
+    <t>(6.22)</t>
+  </si>
+  <si>
+    <t>(5.34)</t>
+  </si>
+  <si>
+    <t>(2.38)</t>
+  </si>
+  <si>
+    <t>0.10%</t>
+  </si>
+  <si>
+    <t>0.71%</t>
+  </si>
+  <si>
+    <t>2.17%</t>
+  </si>
+  <si>
+    <t>(0.52)</t>
+  </si>
+  <si>
+    <t>2.02%</t>
+  </si>
+  <si>
+    <t>3.25%</t>
+  </si>
+  <si>
+    <t>4.10%</t>
+  </si>
+  <si>
+    <t>5.48%</t>
+  </si>
+  <si>
+    <t>(2.16)</t>
+  </si>
+  <si>
+    <t>(2.57)</t>
+  </si>
+  <si>
+    <t>(2.59)</t>
+  </si>
+  <si>
+    <t>(2.85)</t>
+  </si>
+  <si>
+    <t>1.93%</t>
+  </si>
+  <si>
+    <t>2.54%</t>
+  </si>
+  <si>
+    <t>1.92%</t>
+  </si>
+  <si>
+    <t>0.46%</t>
+  </si>
+  <si>
+    <t>(2.76)</t>
+  </si>
+  <si>
+    <t>(2.93)</t>
+  </si>
+  <si>
+    <t>(1.68)</t>
+  </si>
+  <si>
+    <t>(0.30)</t>
+  </si>
+  <si>
+    <t>J=</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>K=</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -1131,7 +1416,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1243,6 +1528,39 @@
     <xf numFmtId="176" fontId="21" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1267,54 +1585,9 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1327,32 +1600,8 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1400,20 +1649,10 @@
     <cellStyle name="壞" xfId="8" builtinId="27" customBuiltin="1"/>
     <cellStyle name="警告文字" xfId="15" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
       </font>
     </dxf>
     <dxf>
@@ -1429,56 +1668,6 @@
     <dxf>
       <font>
         <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
       </font>
     </dxf>
     <dxf>
@@ -1832,30 +2021,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{828DFD01-9D50-4EA6-A7DD-A0B766D34BA5}">
   <dimension ref="A1:N60"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="17.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="8.625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="13.25" style="13" customWidth="1"/>
+    <col min="1" max="2" width="11.33203125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" style="13" customWidth="1"/>
     <col min="6" max="6" width="16" style="8" customWidth="1"/>
-    <col min="7" max="7" width="15.75" style="8" customWidth="1"/>
-    <col min="10" max="10" width="15.375" customWidth="1"/>
-    <col min="11" max="14" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="15.77734375" style="8" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" customWidth="1"/>
+    <col min="11" max="14" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1878,7 +2067,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -1901,7 +2090,7 @@
         <v>0.97742896460482598</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -1924,7 +2113,7 @@
         <v>5.6845064904419997E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -1946,16 +2135,16 @@
       <c r="G5" s="9">
         <v>5.1106356269530005E-4</v>
       </c>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="43"/>
-    </row>
-    <row r="6" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="54"/>
+    </row>
+    <row r="6" spans="1:14" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>3</v>
       </c>
@@ -1996,7 +2185,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>3</v>
       </c>
@@ -2018,10 +2207,10 @@
       <c r="G7" s="10">
         <v>7.9232025762956804E-6</v>
       </c>
-      <c r="I7" s="49">
-        <v>3</v>
-      </c>
-      <c r="J7" s="44" t="s">
+      <c r="I7" s="56">
+        <v>3</v>
+      </c>
+      <c r="J7" s="55" t="s">
         <v>7</v>
       </c>
       <c r="K7" s="14">
@@ -2041,7 +2230,7 @@
         <v>2.3280515551955899E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -2063,8 +2252,8 @@
       <c r="G8" s="10">
         <v>2.184178713642E-4</v>
       </c>
-      <c r="I8" s="38"/>
-      <c r="J8" s="45"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="44"/>
       <c r="K8" s="20" t="str">
         <f>"("&amp;TEXT($F3, "0.00")&amp;")"</f>
         <v>(0.03)</v>
@@ -2082,7 +2271,7 @@
         <v>(1.16)</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>3</v>
       </c>
@@ -2104,8 +2293,8 @@
       <c r="G9" s="9">
         <v>0.34096046080184</v>
       </c>
-      <c r="I9" s="38"/>
-      <c r="J9" s="46" t="s">
+      <c r="I9" s="49"/>
+      <c r="J9" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K9" s="28">
@@ -2125,7 +2314,7 @@
         <v>9.33097832882889E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>3</v>
       </c>
@@ -2147,8 +2336,8 @@
       <c r="G10" s="9">
         <v>1.2141876138480901E-6</v>
       </c>
-      <c r="I10" s="38"/>
-      <c r="J10" s="45"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="44"/>
       <c r="K10" s="22" t="str">
         <f>"("&amp;TEXT($F4,"0.00")&amp;")"</f>
         <v>(3.55)</v>
@@ -2166,7 +2355,7 @@
         <v>(4.41)</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>3</v>
       </c>
@@ -2188,8 +2377,8 @@
       <c r="G11" s="9">
         <v>1.7724280876774E-5</v>
       </c>
-      <c r="I11" s="38"/>
-      <c r="J11" s="47" t="s">
+      <c r="I11" s="49"/>
+      <c r="J11" s="46" t="s">
         <v>9</v>
       </c>
       <c r="K11" s="28">
@@ -2209,7 +2398,7 @@
         <v>7.0029267736333001E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>3</v>
       </c>
@@ -2231,8 +2420,8 @@
       <c r="G12" s="10">
         <v>0.24789234222405299</v>
       </c>
-      <c r="I12" s="39"/>
-      <c r="J12" s="48"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="47"/>
       <c r="K12" s="23" t="str">
         <f>"("&amp;TEXT($F5,"0.00")&amp;")"</f>
         <v>(3.58)</v>
@@ -2250,7 +2439,7 @@
         <v>(3.39)</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>3</v>
       </c>
@@ -2272,10 +2461,10 @@
       <c r="G13" s="10">
         <v>2.5034503907783899E-5</v>
       </c>
-      <c r="I13" s="37">
+      <c r="I13" s="48">
         <v>6</v>
       </c>
-      <c r="J13" s="65" t="s">
+      <c r="J13" s="43" t="s">
         <v>7</v>
       </c>
       <c r="K13" s="14">
@@ -2291,7 +2480,7 @@
         <v>3.0649711185840801E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>3</v>
       </c>
@@ -2313,8 +2502,8 @@
       <c r="G14" s="10">
         <v>9.8533179837500011E-4</v>
       </c>
-      <c r="I14" s="38"/>
-      <c r="J14" s="45"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="44"/>
       <c r="K14" s="20" t="s">
         <v>10</v>
       </c>
@@ -2328,7 +2517,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>6</v>
       </c>
@@ -2350,8 +2539,8 @@
       <c r="G15" s="9">
         <v>0.65423383389473</v>
       </c>
-      <c r="I15" s="38"/>
-      <c r="J15" s="46" t="s">
+      <c r="I15" s="49"/>
+      <c r="J15" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K15" s="28">
@@ -2367,7 +2556,7 @@
         <v>5.3065850483251402E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>6</v>
       </c>
@@ -2389,8 +2578,8 @@
       <c r="G16" s="9">
         <v>2.1961835765053998E-3</v>
       </c>
-      <c r="I16" s="38"/>
-      <c r="J16" s="45"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="44"/>
       <c r="K16" s="22" t="s">
         <v>11</v>
       </c>
@@ -2404,7 +2593,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>6</v>
       </c>
@@ -2426,8 +2615,8 @@
       <c r="G17" s="9">
         <v>8.3279350537053005E-3</v>
       </c>
-      <c r="I17" s="38"/>
-      <c r="J17" s="47" t="s">
+      <c r="I17" s="49"/>
+      <c r="J17" s="46" t="s">
         <v>9</v>
       </c>
       <c r="K17" s="28">
@@ -2443,7 +2632,7 @@
         <v>2.2416139297410601E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>6</v>
       </c>
@@ -2465,8 +2654,8 @@
       <c r="G18" s="10">
         <v>0.18067514945157101</v>
       </c>
-      <c r="I18" s="39"/>
-      <c r="J18" s="48"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="47"/>
       <c r="K18" s="19" t="s">
         <v>12</v>
       </c>
@@ -2480,7 +2669,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>6</v>
       </c>
@@ -2502,10 +2691,10 @@
       <c r="G19" s="10">
         <v>6.0419980721123302E-5</v>
       </c>
-      <c r="I19" s="37">
-        <v>9</v>
-      </c>
-      <c r="J19" s="65" t="s">
+      <c r="I19" s="48">
+        <v>9</v>
+      </c>
+      <c r="J19" s="43" t="s">
         <v>7</v>
       </c>
       <c r="K19" s="14">
@@ -2521,7 +2710,7 @@
         <v>1.5399793559194999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>6</v>
       </c>
@@ -2543,8 +2732,8 @@
       <c r="G20" s="10">
         <v>3.5367985366198001E-3</v>
       </c>
-      <c r="I20" s="38"/>
-      <c r="J20" s="45"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="44"/>
       <c r="K20" s="20" t="s">
         <v>16</v>
       </c>
@@ -2558,7 +2747,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>6</v>
       </c>
@@ -2580,8 +2769,8 @@
       <c r="G21" s="9">
         <v>0.231100321207518</v>
       </c>
-      <c r="I21" s="38"/>
-      <c r="J21" s="46" t="s">
+      <c r="I21" s="49"/>
+      <c r="J21" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K21" s="28">
@@ -2597,7 +2786,7 @@
         <v>4.1963339851818701E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>6</v>
       </c>
@@ -2619,8 +2808,8 @@
       <c r="G22" s="9">
         <v>4.7856639655370002E-4</v>
       </c>
-      <c r="I22" s="38"/>
-      <c r="J22" s="45"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="44"/>
       <c r="K22" s="22" t="s">
         <v>17</v>
       </c>
@@ -2634,7 +2823,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>6</v>
       </c>
@@ -2656,8 +2845,8 @@
       <c r="G23" s="9">
         <v>7.9506872459265999E-3</v>
       </c>
-      <c r="I23" s="38"/>
-      <c r="J23" s="47" t="s">
+      <c r="I23" s="49"/>
+      <c r="J23" s="46" t="s">
         <v>9</v>
       </c>
       <c r="K23" s="28">
@@ -2673,7 +2862,7 @@
         <v>2.6563546292623599E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>6</v>
       </c>
@@ -2695,8 +2884,8 @@
       <c r="G24" s="10">
         <v>0.12891208974354801</v>
       </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="48"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="47"/>
       <c r="K24" s="19" t="s">
         <v>18</v>
       </c>
@@ -2710,7 +2899,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>6</v>
       </c>
@@ -2732,10 +2921,10 @@
       <c r="G25" s="10">
         <v>8.7196464352812999E-3</v>
       </c>
-      <c r="I25" s="37">
+      <c r="I25" s="48">
         <v>12</v>
       </c>
-      <c r="J25" s="65" t="s">
+      <c r="J25" s="43" t="s">
         <v>7</v>
       </c>
       <c r="K25" s="14">
@@ -2751,7 +2940,7 @@
         <v>4.7582304856785398E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>6</v>
       </c>
@@ -2773,8 +2962,8 @@
       <c r="G26" s="10">
         <v>0.208888402471089</v>
       </c>
-      <c r="I26" s="38"/>
-      <c r="J26" s="45"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="44"/>
       <c r="K26" s="20" t="s">
         <v>13</v>
       </c>
@@ -2788,7 +2977,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>9</v>
       </c>
@@ -2810,8 +2999,8 @@
       <c r="G27" s="9">
         <v>0.95805729432186704</v>
       </c>
-      <c r="I27" s="38"/>
-      <c r="J27" s="46" t="s">
+      <c r="I27" s="49"/>
+      <c r="J27" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K27" s="14">
@@ -2827,7 +3016,7 @@
         <v>5.05347405509049E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>9</v>
       </c>
@@ -2849,8 +3038,8 @@
       <c r="G28" s="9">
         <v>1.6370331429953E-3</v>
       </c>
-      <c r="I28" s="38"/>
-      <c r="J28" s="45"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="44"/>
       <c r="K28" s="20" t="s">
         <v>14</v>
       </c>
@@ -2864,7 +3053,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>9</v>
       </c>
@@ -2886,8 +3075,8 @@
       <c r="G29" s="9">
         <v>4.6583346619845003E-3</v>
       </c>
-      <c r="I29" s="38"/>
-      <c r="J29" s="47" t="s">
+      <c r="I29" s="49"/>
+      <c r="J29" s="46" t="s">
         <v>9</v>
       </c>
       <c r="K29" s="28">
@@ -2903,7 +3092,7 @@
         <v>2.9524356941194999E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>9</v>
       </c>
@@ -2925,8 +3114,8 @@
       <c r="G30" s="10">
         <v>0.96471301456515401</v>
       </c>
-      <c r="I30" s="40"/>
-      <c r="J30" s="48"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="47"/>
       <c r="K30" s="34" t="s">
         <v>15</v>
       </c>
@@ -2940,7 +3129,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>9</v>
       </c>
@@ -2967,7 +3156,7 @@
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>9</v>
       </c>
@@ -2994,7 +3183,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <v>9</v>
       </c>
@@ -3021,7 +3210,7 @@
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <v>9</v>
       </c>
@@ -3048,7 +3237,7 @@
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>9</v>
       </c>
@@ -3075,7 +3264,7 @@
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>9</v>
       </c>
@@ -3102,7 +3291,7 @@
       <c r="M36" s="16"/>
       <c r="N36" s="16"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>9</v>
       </c>
@@ -3129,7 +3318,7 @@
       <c r="M37" s="14"/>
       <c r="N37" s="14"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>9</v>
       </c>
@@ -3156,7 +3345,7 @@
       <c r="M38" s="16"/>
       <c r="N38" s="16"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <v>12</v>
       </c>
@@ -3183,7 +3372,7 @@
       <c r="M39" s="14"/>
       <c r="N39" s="14"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <v>12</v>
       </c>
@@ -3210,7 +3399,7 @@
       <c r="M40" s="16"/>
       <c r="N40" s="16"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>12</v>
       </c>
@@ -3237,7 +3426,7 @@
       <c r="M41" s="14"/>
       <c r="N41" s="14"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>12</v>
       </c>
@@ -3264,7 +3453,7 @@
       <c r="M42" s="16"/>
       <c r="N42" s="16"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>12</v>
       </c>
@@ -3291,7 +3480,7 @@
       <c r="M43" s="14"/>
       <c r="N43" s="14"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>12</v>
       </c>
@@ -3318,7 +3507,7 @@
       <c r="M44" s="16"/>
       <c r="N44" s="16"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
         <v>12</v>
       </c>
@@ -3345,7 +3534,7 @@
       <c r="M45" s="14"/>
       <c r="N45" s="14"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
         <v>12</v>
       </c>
@@ -3372,7 +3561,7 @@
       <c r="M46" s="16"/>
       <c r="N46" s="16"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
         <v>12</v>
       </c>
@@ -3399,7 +3588,7 @@
       <c r="M47" s="14"/>
       <c r="N47" s="14"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>12</v>
       </c>
@@ -3426,7 +3615,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="16"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>12</v>
       </c>
@@ -3453,7 +3642,7 @@
       <c r="M49" s="14"/>
       <c r="N49" s="14"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>12</v>
       </c>
@@ -3480,61 +3669,61 @@
       <c r="M50" s="16"/>
       <c r="N50" s="16"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K51" s="14"/>
       <c r="L51" s="14"/>
       <c r="M51" s="14"/>
       <c r="N51" s="14"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K52" s="16"/>
       <c r="L52" s="16"/>
       <c r="M52" s="16"/>
       <c r="N52" s="16"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K53" s="14"/>
       <c r="L53" s="14"/>
       <c r="M53" s="14"/>
       <c r="N53" s="14"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K54" s="16"/>
       <c r="L54" s="16"/>
       <c r="M54" s="16"/>
       <c r="N54" s="16"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K55" s="14"/>
       <c r="L55" s="14"/>
       <c r="M55" s="14"/>
       <c r="N55" s="14"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K56" s="16"/>
       <c r="L56" s="16"/>
       <c r="M56" s="16"/>
       <c r="N56" s="16"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K57" s="14"/>
       <c r="L57" s="14"/>
       <c r="M57" s="14"/>
       <c r="N57" s="14"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K58" s="16"/>
       <c r="L58" s="16"/>
       <c r="M58" s="16"/>
       <c r="N58" s="16"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K59" s="14"/>
       <c r="L59" s="14"/>
       <c r="M59" s="14"/>
       <c r="N59" s="14"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K60" s="16"/>
       <c r="L60" s="16"/>
       <c r="M60" s="16"/>
@@ -3547,12 +3736,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="I19:I24"/>
     <mergeCell ref="I25:I30"/>
     <mergeCell ref="I5:N5"/>
     <mergeCell ref="J7:J8"/>
@@ -3565,18 +3748,24 @@
     <mergeCell ref="J25:J26"/>
     <mergeCell ref="J27:J28"/>
     <mergeCell ref="J29:J30"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="I19:I24"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="E2:E1048576">
-    <cfRule type="cellIs" dxfId="23" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1048576">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3588,29 +3777,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60641E96-17E1-4C28-95A7-3B3EADA10A6C}">
   <dimension ref="A1:N50"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.625" customWidth="1"/>
+    <col min="1" max="2" width="10.6640625" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="5" max="5" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.125" customWidth="1"/>
-    <col min="10" max="10" width="15.25" customWidth="1"/>
-    <col min="11" max="14" width="11.375" customWidth="1"/>
+    <col min="9" max="9" width="7.109375" customWidth="1"/>
+    <col min="10" max="10" width="15.21875" customWidth="1"/>
+    <col min="11" max="14" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -3633,7 +3822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -3648,7 +3837,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -3662,16 +3851,16 @@
       <c r="E4" s="11"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="I4" s="41" t="s">
+      <c r="I4" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="43"/>
-    </row>
-    <row r="5" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="54"/>
+    </row>
+    <row r="5" spans="1:14" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -3704,7 +3893,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>3</v>
       </c>
@@ -3718,10 +3907,10 @@
       <c r="E6" s="12"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
-      <c r="I6" s="49">
-        <v>3</v>
-      </c>
-      <c r="J6" s="44" t="s">
+      <c r="I6" s="56">
+        <v>3</v>
+      </c>
+      <c r="J6" s="55" t="s">
         <v>7</v>
       </c>
       <c r="K6" s="14"/>
@@ -3729,7 +3918,7 @@
       <c r="M6" s="14"/>
       <c r="N6" s="26"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>3</v>
       </c>
@@ -3743,14 +3932,14 @@
       <c r="E7" s="12"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="66"/>
-      <c r="L7" s="66"/>
-      <c r="M7" s="66"/>
-      <c r="N7" s="67"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I7" s="49"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="27"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -3764,16 +3953,16 @@
       <c r="E8" s="12"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="46" t="s">
+      <c r="I8" s="49"/>
+      <c r="J8" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
-      <c r="N8" s="56"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="26"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>3</v>
       </c>
@@ -3787,14 +3976,14 @@
       <c r="E9" s="11"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="57"/>
-      <c r="M9" s="57"/>
-      <c r="N9" s="58"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I9" s="49"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="30"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>3</v>
       </c>
@@ -3808,16 +3997,16 @@
       <c r="E10" s="11"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="68"/>
-      <c r="L10" s="68"/>
-      <c r="M10" s="68"/>
-      <c r="N10" s="56"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I10" s="49"/>
+      <c r="J10" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="26"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>3</v>
       </c>
@@ -3831,14 +4020,14 @@
       <c r="E11" s="11"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="69"/>
-      <c r="L11" s="69"/>
-      <c r="M11" s="69"/>
-      <c r="N11" s="70"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I11" s="50"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="31"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>3</v>
       </c>
@@ -3852,18 +4041,18 @@
       <c r="E12" s="12"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
-      <c r="I12" s="37">
+      <c r="I12" s="48">
         <v>6</v>
       </c>
-      <c r="J12" s="65" t="s">
+      <c r="J12" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="K12" s="68"/>
-      <c r="L12" s="68"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="56"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="26"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>3</v>
       </c>
@@ -3877,14 +4066,14 @@
       <c r="E13" s="12"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="66"/>
-      <c r="L13" s="66"/>
-      <c r="M13" s="66"/>
-      <c r="N13" s="67"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I13" s="49"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="27"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>3</v>
       </c>
@@ -3898,16 +4087,16 @@
       <c r="E14" s="12"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="46" t="s">
+      <c r="I14" s="49"/>
+      <c r="J14" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="68"/>
-      <c r="L14" s="68"/>
-      <c r="M14" s="68"/>
-      <c r="N14" s="56"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="26"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>6</v>
       </c>
@@ -3921,14 +4110,14 @@
       <c r="E15" s="11"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="57"/>
-      <c r="M15" s="57"/>
-      <c r="N15" s="58"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I15" s="49"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="30"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>6</v>
       </c>
@@ -3942,16 +4131,16 @@
       <c r="E16" s="11"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="68"/>
-      <c r="L16" s="68"/>
-      <c r="M16" s="68"/>
-      <c r="N16" s="56"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I16" s="49"/>
+      <c r="J16" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="26"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>6</v>
       </c>
@@ -3965,14 +4154,14 @@
       <c r="E17" s="11"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="69"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="72"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I17" s="50"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="32"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>6</v>
       </c>
@@ -3986,18 +4175,18 @@
       <c r="E18" s="12"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
-      <c r="I18" s="37">
-        <v>9</v>
-      </c>
-      <c r="J18" s="65" t="s">
+      <c r="I18" s="48">
+        <v>9</v>
+      </c>
+      <c r="J18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="K18" s="68"/>
-      <c r="L18" s="68"/>
-      <c r="M18" s="68"/>
-      <c r="N18" s="56"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="26"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>6</v>
       </c>
@@ -4011,14 +4200,14 @@
       <c r="E19" s="12"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="67"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I19" s="49"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="27"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>6</v>
       </c>
@@ -4032,16 +4221,16 @@
       <c r="E20" s="12"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="46" t="s">
+      <c r="I20" s="49"/>
+      <c r="J20" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="68"/>
-      <c r="L20" s="68"/>
-      <c r="M20" s="68"/>
-      <c r="N20" s="56"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="26"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>6</v>
       </c>
@@ -4055,14 +4244,14 @@
       <c r="E21" s="11"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="57"/>
-      <c r="N21" s="58"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I21" s="49"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="30"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>6</v>
       </c>
@@ -4076,16 +4265,16 @@
       <c r="E22" s="11"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="68"/>
-      <c r="L22" s="68"/>
-      <c r="M22" s="68"/>
-      <c r="N22" s="56"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I22" s="49"/>
+      <c r="J22" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="26"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>6</v>
       </c>
@@ -4099,14 +4288,14 @@
       <c r="E23" s="11"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="48"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="69"/>
-      <c r="M23" s="69"/>
-      <c r="N23" s="72"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I23" s="50"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="32"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>6</v>
       </c>
@@ -4120,18 +4309,18 @@
       <c r="E24" s="12"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
-      <c r="I24" s="37">
+      <c r="I24" s="48">
         <v>12</v>
       </c>
-      <c r="J24" s="65" t="s">
+      <c r="J24" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="K24" s="68"/>
-      <c r="L24" s="68"/>
-      <c r="M24" s="68"/>
-      <c r="N24" s="56"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="26"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>6</v>
       </c>
@@ -4145,14 +4334,14 @@
       <c r="E25" s="12"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="66"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="66"/>
-      <c r="N25" s="73"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I25" s="49"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="33"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>6</v>
       </c>
@@ -4166,16 +4355,16 @@
       <c r="E26" s="12"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="46" t="s">
+      <c r="I26" s="49"/>
+      <c r="J26" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="68"/>
-      <c r="L26" s="68"/>
-      <c r="M26" s="68"/>
-      <c r="N26" s="56"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="26"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>9</v>
       </c>
@@ -4189,14 +4378,14 @@
       <c r="E27" s="11"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="66"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="73"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I27" s="49"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="33"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>9</v>
       </c>
@@ -4210,16 +4399,16 @@
       <c r="E28" s="11"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="K28" s="68"/>
-      <c r="L28" s="68"/>
-      <c r="M28" s="68"/>
-      <c r="N28" s="56"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I28" s="49"/>
+      <c r="J28" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="26"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>9</v>
       </c>
@@ -4233,14 +4422,14 @@
       <c r="E29" s="11"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="48"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="47"/>
       <c r="K29" s="34"/>
       <c r="L29" s="35"/>
       <c r="M29" s="35"/>
       <c r="N29" s="36"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>9</v>
       </c>
@@ -4255,7 +4444,7 @@
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>9</v>
       </c>
@@ -4270,7 +4459,7 @@
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>9</v>
       </c>
@@ -4285,7 +4474,7 @@
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <v>9</v>
       </c>
@@ -4300,7 +4489,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <v>9</v>
       </c>
@@ -4315,7 +4504,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>9</v>
       </c>
@@ -4330,7 +4519,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>9</v>
       </c>
@@ -4345,7 +4534,7 @@
       <c r="F36" s="10"/>
       <c r="G36" s="10"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>9</v>
       </c>
@@ -4360,7 +4549,7 @@
       <c r="F37" s="10"/>
       <c r="G37" s="10"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>9</v>
       </c>
@@ -4375,7 +4564,7 @@
       <c r="F38" s="10"/>
       <c r="G38" s="10"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <v>12</v>
       </c>
@@ -4390,7 +4579,7 @@
       <c r="F39" s="9"/>
       <c r="G39" s="9"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <v>12</v>
       </c>
@@ -4405,7 +4594,7 @@
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>12</v>
       </c>
@@ -4420,7 +4609,7 @@
       <c r="F41" s="9"/>
       <c r="G41" s="9"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>12</v>
       </c>
@@ -4435,7 +4624,7 @@
       <c r="F42" s="10"/>
       <c r="G42" s="10"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>12</v>
       </c>
@@ -4450,7 +4639,7 @@
       <c r="F43" s="10"/>
       <c r="G43" s="10"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>12</v>
       </c>
@@ -4465,7 +4654,7 @@
       <c r="F44" s="10"/>
       <c r="G44" s="10"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
         <v>12</v>
       </c>
@@ -4480,7 +4669,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
         <v>12</v>
       </c>
@@ -4495,7 +4684,7 @@
       <c r="F46" s="9"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
         <v>12</v>
       </c>
@@ -4510,7 +4699,7 @@
       <c r="F47" s="9"/>
       <c r="G47" s="9"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>12</v>
       </c>
@@ -4525,7 +4714,7 @@
       <c r="F48" s="10"/>
       <c r="G48" s="10"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>12</v>
       </c>
@@ -4540,7 +4729,7 @@
       <c r="F49" s="10"/>
       <c r="G49" s="10"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>12</v>
       </c>
@@ -4557,6 +4746,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="I6:I11"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="J10:J11"/>
     <mergeCell ref="I24:I29"/>
     <mergeCell ref="J24:J25"/>
     <mergeCell ref="J26:J27"/>
@@ -4569,37 +4764,18 @@
     <mergeCell ref="J18:J19"/>
     <mergeCell ref="J20:J21"/>
     <mergeCell ref="J22:J23"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="I6:I11"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="J10:J11"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="E2">
-    <cfRule type="cellIs" dxfId="20" priority="11" operator="lessThan">
+  <conditionalFormatting sqref="E2:E50">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
-    <cfRule type="cellIs" dxfId="18" priority="10" operator="lessThan">
-      <formula>0.05</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E50">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G50">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="G2:G50">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4610,29 +4786,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA12766-CA57-4195-AB5D-D953190D2612}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.375" customWidth="1"/>
-    <col min="6" max="6" width="9.75" customWidth="1"/>
-    <col min="7" max="7" width="10.75" customWidth="1"/>
-    <col min="8" max="8" width="2.75" customWidth="1"/>
-    <col min="9" max="9" width="7.25" customWidth="1"/>
-    <col min="10" max="10" width="14.875" customWidth="1"/>
-    <col min="11" max="14" width="12.25" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" customWidth="1"/>
+    <col min="8" max="8" width="2.77734375" customWidth="1"/>
+    <col min="9" max="9" width="7.21875" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" customWidth="1"/>
+    <col min="11" max="14" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -4654,16 +4830,16 @@
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="64" t="s">
+      <c r="I2" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64"/>
-    </row>
-    <row r="3" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+    </row>
+    <row r="3" spans="1:14" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -4685,26 +4861,26 @@
       <c r="G3" s="9">
         <v>0.89865125913546695</v>
       </c>
-      <c r="I3" s="52" t="s">
+      <c r="I3" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="53" t="s">
+      <c r="J3" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="59">
-        <v>3</v>
-      </c>
-      <c r="L3" s="59">
+      <c r="K3" s="40">
+        <v>3</v>
+      </c>
+      <c r="L3" s="40">
         <v>6</v>
       </c>
-      <c r="M3" s="59">
-        <v>9</v>
-      </c>
-      <c r="N3" s="60">
+      <c r="M3" s="40">
+        <v>9</v>
+      </c>
+      <c r="N3" s="41">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -4726,21 +4902,21 @@
       <c r="G4" s="9">
         <v>3.4952799955571198E-3</v>
       </c>
-      <c r="I4" s="61">
-        <v>3</v>
-      </c>
-      <c r="J4" s="44" t="s">
+      <c r="I4" s="57">
+        <v>3</v>
+      </c>
+      <c r="J4" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="54">
+      <c r="K4" s="14">
         <f>E3</f>
         <v>1.2676155267131099E-3</v>
       </c>
-      <c r="L4" s="54">
+      <c r="L4" s="14">
         <f>E6</f>
         <v>-2.2454643896498601E-3</v>
       </c>
-      <c r="M4" s="54">
+      <c r="M4" s="14">
         <f>E9</f>
         <v>-4.9802207879865498E-3</v>
       </c>
@@ -4749,7 +4925,7 @@
         <v>3.1250864080159101E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -4771,8 +4947,8 @@
       <c r="G5" s="9">
         <v>3.7518090649497199E-4</v>
       </c>
-      <c r="I5" s="62"/>
-      <c r="J5" s="45"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="44"/>
       <c r="K5" s="20">
         <f>F3</f>
         <v>0.127652013401201</v>
@@ -4790,7 +4966,7 @@
         <v>1.9490597473919499E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>3</v>
       </c>
@@ -4812,19 +4988,19 @@
       <c r="G6" s="10">
         <v>0.84773787571883197</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="46" t="s">
+      <c r="I6" s="58"/>
+      <c r="J6" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="55">
+      <c r="K6" s="28">
         <f>E4</f>
         <v>2.4591457834495602E-2</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="28">
         <f>E7</f>
         <v>4.6514485130783302E-2</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="28">
         <f>E10</f>
         <v>6.2453828535481599E-2</v>
       </c>
@@ -4833,7 +5009,7 @@
         <v>3.1250864080159101E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>3</v>
       </c>
@@ -4855,26 +5031,26 @@
       <c r="G7" s="10">
         <v>1.7170331339624899E-4</v>
       </c>
-      <c r="I7" s="62"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="57">
+      <c r="I7" s="58"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="22">
         <f>F4</f>
         <v>2.9832338535301401</v>
       </c>
-      <c r="L7" s="57">
+      <c r="L7" s="22">
         <f>F7</f>
         <v>3.8905337675188099</v>
       </c>
-      <c r="M7" s="57">
+      <c r="M7" s="22">
         <f>F10</f>
         <v>4.20880434785182</v>
       </c>
-      <c r="N7" s="58">
+      <c r="N7" s="30">
         <f>F13</f>
         <v>3.7415387914354601</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -4896,19 +5072,19 @@
       <c r="G8" s="10">
         <v>9.0227491087471003E-11</v>
       </c>
-      <c r="I8" s="62"/>
-      <c r="J8" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="55">
+      <c r="I8" s="58"/>
+      <c r="J8" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="28">
         <f>E5</f>
         <v>2.3323842307782498E-2</v>
       </c>
-      <c r="L8" s="55">
+      <c r="L8" s="28">
         <f>E8</f>
         <v>4.8759949520433103E-2</v>
       </c>
-      <c r="M8" s="55">
+      <c r="M8" s="28">
         <f>E11</f>
         <v>6.7434049323468095E-2</v>
       </c>
@@ -4917,7 +5093,7 @@
         <v>3.1250864080159101E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>3</v>
       </c>
@@ -4939,8 +5115,8 @@
       <c r="G9" s="9">
         <v>0.70385043948405301</v>
       </c>
-      <c r="I9" s="63"/>
-      <c r="J9" s="48"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="47"/>
       <c r="K9" s="23">
         <f>F5</f>
         <v>3.6673643552384498</v>
@@ -4958,7 +5134,7 @@
         <v>7.0267777188403997</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>3</v>
       </c>
@@ -4981,7 +5157,7 @@
         <v>5.3598713981954997E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>3</v>
       </c>
@@ -5004,7 +5180,7 @@
         <v>4.6078621241686099E-14</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>3</v>
       </c>
@@ -5027,7 +5203,7 @@
         <v>0.98448708216231096</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>3</v>
       </c>
@@ -5050,7 +5226,7 @@
         <v>2.9983269664811098E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>3</v>
       </c>
@@ -5073,24 +5249,24 @@
         <v>2.2733299034642299E-10</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="50"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="51" t="s">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="37"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="37"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>5</v>
       </c>
@@ -5112,16 +5288,16 @@
       <c r="G18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I18" s="64" t="s">
+      <c r="I18" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="64"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="64"/>
-    </row>
-    <row r="19" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="60"/>
+    </row>
+    <row r="19" spans="1:14" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>3</v>
       </c>
@@ -5143,26 +5319,26 @@
       <c r="G19" s="9">
         <v>0.26158835276995202</v>
       </c>
-      <c r="I19" s="52" t="s">
+      <c r="I19" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="J19" s="53" t="s">
+      <c r="J19" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="K19" s="59">
-        <v>3</v>
-      </c>
-      <c r="L19" s="59">
+      <c r="K19" s="40">
+        <v>3</v>
+      </c>
+      <c r="L19" s="40">
         <v>6</v>
       </c>
-      <c r="M19" s="59">
-        <v>9</v>
-      </c>
-      <c r="N19" s="60">
+      <c r="M19" s="40">
+        <v>9</v>
+      </c>
+      <c r="N19" s="41">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>3</v>
       </c>
@@ -5184,21 +5360,21 @@
       <c r="G20" s="9">
         <v>1.9022683024534E-6</v>
       </c>
-      <c r="I20" s="61">
-        <v>3</v>
-      </c>
-      <c r="J20" s="44" t="s">
+      <c r="I20" s="57">
+        <v>3</v>
+      </c>
+      <c r="J20" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="K20" s="54">
+      <c r="K20" s="14">
         <f>E19</f>
         <v>8.9648117847710498E-3</v>
       </c>
-      <c r="L20" s="54">
+      <c r="L20" s="14">
         <f>E22</f>
         <v>1.9186431825705601E-2</v>
       </c>
-      <c r="M20" s="54">
+      <c r="M20" s="14">
         <f>E25</f>
         <v>3.1641119197947001E-2</v>
       </c>
@@ -5207,7 +5383,7 @@
         <v>5.52136466982436E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>3</v>
       </c>
@@ -5229,8 +5405,8 @@
       <c r="G21" s="9">
         <v>1.41941805723813E-7</v>
       </c>
-      <c r="I21" s="62"/>
-      <c r="J21" s="45"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="44"/>
       <c r="K21" s="20">
         <f>F19</f>
         <v>1.1263240230215701</v>
@@ -5248,7 +5424,7 @@
         <v>3.6216418290305401</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>3</v>
       </c>
@@ -5270,19 +5446,19 @@
       <c r="G22" s="10">
         <v>5.4729223964147297E-2</v>
       </c>
-      <c r="I22" s="62"/>
-      <c r="J22" s="46" t="s">
+      <c r="I22" s="58"/>
+      <c r="J22" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="55">
+      <c r="K22" s="28">
         <f>E20</f>
         <v>3.6456284904080198E-2</v>
       </c>
-      <c r="L22" s="55">
+      <c r="L22" s="28">
         <f>E23</f>
         <v>7.1496430351053006E-2</v>
       </c>
-      <c r="M22" s="55">
+      <c r="M22" s="28">
         <f>E26</f>
         <v>9.9917898969015498E-2</v>
       </c>
@@ -5291,7 +5467,7 @@
         <v>0.119470995092858</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>3</v>
       </c>
@@ -5313,26 +5489,26 @@
       <c r="G23" s="10">
         <v>2.8649193162989599E-10</v>
       </c>
-      <c r="I23" s="62"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="57">
+      <c r="I23" s="58"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="22">
         <f>F20</f>
         <v>4.9316087626070901</v>
       </c>
-      <c r="L23" s="57">
+      <c r="L23" s="22">
         <f>F23</f>
         <v>6.7041206290680799</v>
       </c>
-      <c r="M23" s="57">
+      <c r="M23" s="22">
         <f>F26</f>
         <v>7.7215872485542496</v>
       </c>
-      <c r="N23" s="58">
+      <c r="N23" s="30">
         <f>F29</f>
         <v>7.50325410032573</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>3</v>
       </c>
@@ -5354,19 +5530,19 @@
       <c r="G24" s="10">
         <v>6.3190312413867199E-15</v>
       </c>
-      <c r="I24" s="62"/>
-      <c r="J24" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="55">
+      <c r="I24" s="58"/>
+      <c r="J24" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="28">
         <f>E21</f>
         <v>2.74914731193092E-2</v>
       </c>
-      <c r="L24" s="55">
+      <c r="L24" s="28">
         <f>E24</f>
         <v>5.2309998525347297E-2</v>
       </c>
-      <c r="M24" s="55">
+      <c r="M24" s="28">
         <f>E27</f>
         <v>6.8276779771068496E-2</v>
       </c>
@@ -5375,7 +5551,7 @@
         <v>6.4257348394614999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>3</v>
       </c>
@@ -5397,8 +5573,8 @@
       <c r="G25" s="9">
         <v>1.01161296606066E-2</v>
       </c>
-      <c r="I25" s="63"/>
-      <c r="J25" s="48"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="47"/>
       <c r="K25" s="23">
         <f>F21</f>
         <v>5.48900911918963</v>
@@ -5416,7 +5592,7 @@
         <v>7.1660071590778198</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>3</v>
       </c>
@@ -5439,7 +5615,7 @@
         <v>1.00440591326992E-12</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>3</v>
       </c>
@@ -5462,7 +5638,7 @@
         <v>1.0271044282789199E-15</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>3</v>
       </c>
@@ -5485,7 +5661,7 @@
         <v>3.8989453950004702E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>3</v>
       </c>
@@ -5508,7 +5684,7 @@
         <v>3.7410479353997401E-12</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>3</v>
       </c>
@@ -5533,11 +5709,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="I20:I25"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="I18:N18"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
@@ -5545,61 +5716,946 @@
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
+    <mergeCell ref="I20:I25"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="I18:N18"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="E2">
-    <cfRule type="cellIs" dxfId="14" priority="11" operator="lessThan">
+  <conditionalFormatting sqref="E2:E14">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
-    <cfRule type="cellIs" dxfId="12" priority="10" operator="lessThan">
+  <conditionalFormatting sqref="E18:E30">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G14">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E18">
-    <cfRule type="cellIs" dxfId="11" priority="8" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="9" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G18">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="lessThan">
-      <formula>0.05</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E14">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G14">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThan">
-      <formula>0.05</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19:E30">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G19:G30">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="G18:G30">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8A0F7C-8834-41CC-A062-10334C6CB4AB}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" style="61" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" style="61" customWidth="1"/>
+    <col min="3" max="6" width="11.33203125" style="61" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="10" max="13" width="12.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="49"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" s="49"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="M4" s="29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="49"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="L6" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" s="29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="50"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="50"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="M8" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="49"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="49"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="L10" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="M10" s="29" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="49"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="49"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="M11" s="30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="K12" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="L12" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="M12" s="26" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="50"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="50"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="M13" s="32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="H14" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="M14" s="26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="49"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="49"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="M15" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="K16" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="L16" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="M16" s="29" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="49"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="49"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="M17" s="30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="H18" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="K18" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="L18" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="M18" s="26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="50"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="H19" s="50"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="L19" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="M19" s="32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="M20" s="29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="49"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="49"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="M21" s="33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="I22" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="M22" s="29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="49"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="H23" s="49"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="M23" s="33" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="H24" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="M24" s="26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="51"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="51"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="K25" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="L25" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="M25" s="36" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="H14:H19"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="H20:H25"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="H8:H13"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+  </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>